--- a/sermoes/sermoes_fdqc_preenchida.xlsx
+++ b/sermoes/sermoes_fdqc_preenchida.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como preencher" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sermões'!$A$1:$L$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sermões'!$A$1:$M$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -77,9 +77,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L241"/>
+  <dimension ref="A1:M241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -461,6 +459,7 @@
     <col width="70" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -524,6 +523,11 @@
           <t>Link (YouTube)</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>NotebookLM (textos citados)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -574,12 +578,12 @@
           <t>…es no sermão do monte. Bom dia, irmãos! Tudo bem com vocês? Mateus, capítulo 7, versículo 13 ao 29. Nessa manhã o tema da nossa mensagem é as duas possibilidades. Então encerramos o sermão do monte olhando para as várias duas…</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/as-duas-possibilidades-fabiano-krehnke-serie-a-vida-no-reino</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=rZwTxnlLEC4</t>
         </is>
@@ -634,12 +638,12 @@
           <t>…uanto o sermão do monte. Então vamos ler a palavra de Deus. Mateus capítulo 7, se você vai ler no seu aplicativo, eu estou na NVT. Eu gosto da NVT, tá bom? Um dia a gente conversa sobre a versão bíblica, tá? Hoje a gente só va…</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/as-leis-sobre-os-relacionamentos-interpessoais-dayse-fontoura-serie-a-vida-no-reino</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Lxr1G6BUPdg</t>
         </is>
@@ -694,12 +698,12 @@
           <t>…er a leitura bíblica, fazer a leitura bíblica dessa amanhã. Mateus no capítulo 6, evangelho de Mateus, capítulo 6, dos versos 19 até o 34. Então, se você tenha sua bíblica aí, tome em ela em suas mãos, senão você pode acompanh…</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/tesouros-senhores-e-ansiedades-fabiano-krehnke-serie-a-vida-no-reino</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=curdg8ohOUg</t>
         </is>
@@ -754,12 +758,12 @@
           <t>…disciplinas espirituais ou hipócritas que está no livro de Mateus, do capítulo 6, versículo 1, ao versículo 18. Então você pode pegar a sua bíblia para lermos juntos ou você se atentar aqui na projeção. Vamos ler junto depois…</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/disciplinas-espirituais-ou-hipocritas-leandro-alves-serie-a-vida-no-reino</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Y6d6dM7EQRg</t>
         </is>
@@ -814,12 +818,12 @@
           <t>…monte. Se você quiser já indo à sua abrindo a sua bíblia em Mateus, capítulo 5, hoje nós vamos meditar do versículo 31 ao 48. Para relembrar só na semana passada, nós ainda estamos sábamos do capítulo 5 e o Felipe terminou fal…</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/podcastfinal-0909</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=FTmwdbJU2cU</t>
         </is>
@@ -874,12 +878,12 @@
           <t>…r Jesus, seja uma verdade nossa vida. Abri comigo do Abib e Mateus, capítulo 5 por gentileza. Eu quero ler com vocês na nossa leitura Bíblica dessa manhã, a aportação que compõe do verso 17 até o verso 30. Vamos ler do 17 ao 3…</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/excedendo-em-justica-felipe-bartoszewski-serie-a-vida-no-reino</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jhLPUSBM71s</t>
         </is>
@@ -934,12 +938,12 @@
           <t>…a série que estamos na terceira palavra, temos estudado aí, Mateus 5, começo do capítulo 5. E nessa semana, então, após a semana passada, temos falado sobre as bem-aventuranças. Um texto tão importante, tem falado comigo muito…</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/cristaos-influenciadores-fabiano-krehnke-serie-a-vida-no-reino</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=4ujhKKLkRs0</t>
         </is>
@@ -994,12 +998,12 @@
           <t>…rsículos apenas e hoje eu estarei passando aí do 3 ao 12 de Mateus 5, são as muito conhecidas, bem aventuranças, né? Então nós queremos passar por esse texto bíblico ouvindo a voz do Senhor para falar com nós com na nossa prát…</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/as-normas-do-reino-fabiano-krehnke-serie-a-vida-no-reino</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=v9wf7obc3pw</t>
         </is>
@@ -1054,12 +1058,12 @@
           <t>…ara as multidões. De acordo com o texto que nós vemos aqui, Mateus 5, verse 1 e 2, nós vamos ficar apenas desses dois versos para introdução, ele diz assim, vendas multidões, Jesus subiu ao monte e se acentou. Seus discípulos…</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-formacao-crista-leandro-alves-serie-a-vida-no-reino</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=l2e-XDRkwl4</t>
         </is>
@@ -1109,12 +1113,12 @@
           <t>…sua mão, e gássio do seu lugar, primeira carta de Paulo aos corintos, capítulo 1. Hoje nós damos início a uma nova série de exposições bíblicas. Nesta tão importante epístula ou carta de Paulo, a igreja que estava em corinto.…</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/uma-igreja-improvavel-leandro-vieira-introducao-a-1-corintios-serie-em-cristo-no-mundo</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=KO4PAZwqbjU</t>
         </is>
@@ -1164,12 +1168,12 @@
           <t>…eza que seremos edificados. Ega-se do seu lugar, por favor. Eclesiastes, capítulo 1, nós vamos ler hoje apenas o versículo 1. Deixe-me ressaltar uma vez mais. Cultive o bom hábito de trazer a palavra de Deus nesse formato para o cu…</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/as-aparencias-enganam-leandro-vieira-serie-vanitas-vanitatum</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=0z1Lwhhc5U0</t>
         </is>
@@ -1219,12 +1223,12 @@
           <t>…gan, e agora a gente vai aí para cerca de 12 exposições, 12 capítulos sobre o livro de galatas e hoje eu gostaria de trazer uma introdução com vocês. E dentro dessa introdução eu queria abordar com vocês um pouco sobre o context…</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/panorama-e-introducao-a-carta-aos-galatas-felipe-bartoszewski-serie-anatema-o-outro-evangelho</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=MuzYRtT0D9k</t>
         </is>
@@ -1274,12 +1278,12 @@
           <t>…nessa ocasião, numa quase que sequência, eu li a carta aos Ephesios inteiros, seis capítulos aproximadamente 50 vezes, foram 46 seu nome engano, vezes seguidas, lendo a carta aos Ephesios e meditando naquilo, não uma leitura su…</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/pensando-falando-e-vivendo-introducao-fabiano-khrenke-serie-efesios</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=mvKiCXsW8vw</t>
         </is>
@@ -1316,12 +1320,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>At 16.6ss (contexto da igreja de Filipos)</t>
+          <t>At 16.11-40</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1329,14 +1333,19 @@
           <t>…lônia, como havia falado agora pouco, isso está no livro de Atos, capítulo 16, verso 21. O que é uma colônia? Uma colônia nada mais é do que uma réplica menor da cidade de Roma, por isso eles eram chamados os filipos como um…</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20300707-alves-serie-fp-introducao-audio</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=dZfFuLbbvLs</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Atos 16:11-40; Filipenses 2:5-11</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1393,12 @@
           <t>…enhor para a Conosco, e o texto básico que nós vamos usar é Marcos, cápitulo 16, do verso 15 ao 20. Nós vamos darem fazer um especial ao versículo 15, 16 e o 20. Mas vamos respeitar a leitura do texto como um todo nesse aspect…</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/evangelizando-com-ousadia-felipe-garrote-serie-o-evangelho-na-vida</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=WPQF_ND8DzQ</t>
         </is>
@@ -1439,12 +1448,12 @@
           <t>…ra que vocês fossem abrindo as suas bíblias no Evangelho de Lucas, do capítulo 18, versículo 18. Nós leremos esse texto do 18 ao 30 e depois nós pularemos do 19 e leremos do 1 ao 10. Todo mundo encontrou? Então no Evangelho d…</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/contribuindo-com-generosidade-lucas-gregory-serie-o-evangelho-na-vida</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=VhRuTooQsBM</t>
         </is>
@@ -1481,12 +1490,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Dt 4.39</t>
+          <t>Dt 4.39; Cl 1.15-23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1494,14 +1503,19 @@
           <t>…a os interesses de Cristo e para o bem do mundo. O livro do Deuteronômio, no capítulo 4, versículo de número 39. Portanto, reconheçam este fato e guardem no firmemente na memória. O Senhor é Deus nos céus e na Terra e não há out…</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-divindade-de-jesus-a-gloria-do-filho-de-deus-lucas-gregory-serie-a-pessoa-do-evangelho</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jBSX7_bbGc0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Deuteronômio 4:39; Colossenses 1:15-23</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1563,12 @@
           <t>…mbros. Então, falaremos sobre essa realidade que Paulo, aos corintios, primeira carta de Paulo aos corintos capítulos doze, então reflete. Tiraremos algumas lições importantes desse texto bíblico. Eu gostaria de pedir que voc…</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/um-corpo-muitos-membros-pr-fabiano-krehnke</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ef_VLwVdLe4</t>
         </is>
@@ -1609,12 +1623,12 @@
           <t>…na liturabíblica de hoje. Evangelho, segundo após o Lujão, capítulo 20, Evangelho de Lujão 20, do 1 ao 18. No primeiro dia da semana de Madrugada, quando ainda estava escuro, Maria Madalena foi autúmulo e viu que a pedra da ent…</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/jesus-ressuscitou-voce-consegue-ver-fabiano-krehnke-serie-prepare-o-coracao-para-a-pascoa</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=VB8EyPgHqSw</t>
         </is>
@@ -1669,12 +1683,12 @@
           <t>…sso sermão em titulado Ozzana, o paradoxo do reino, está em marcos no capítulo 11 e do versículo 1 ao versículo 11. Eu gostaria que você ficasse de pé e pudéssemos ler juntos este texto, esta porção das escrituras. Vamos junto…</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/5a61a808-56b8-44b5-be0c-2f7803897e1f</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=AyoqN6EvOQ4</t>
         </is>
@@ -1729,12 +1743,12 @@
           <t>…ara o bem do mundo. Você é que você abri-se à sua Bíblia em João, no Evangelho de João, no capítulo 11, no verso 38. Então, abra a sua Bíblia em João, no capítulo 11, no verso 38. João, no verso 38, vamos ler até o capítulo…</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-vida-apos-a-morte-leivison-rosa-serie-prepare-o-coracao-para-a-pascoa</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=5_Os9ImdPaQ</t>
         </is>
@@ -1789,12 +1803,12 @@
           <t>…amar você para compartilhar uma palavra, abra sua Bíblia em João, o evangelho de João, capítulo 10, se você puder esteja de pé, em seu lugar, a medida que você encontra. Enjoem, enquanto você abra sua Bíblia, irmãos, a gente…</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/ele-habitou-entre-nos-felipe-barros</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=dKayzNrTsPo</t>
         </is>
@@ -1849,12 +1863,12 @@
           <t>…suas bíblas e se colocar em pé, por favor. Lá em primeira a João, capítulo 4 versículos 10, a gente vai dizer isso ao 10 e o 19. Hoje nós vamos tratar sobre as disciplinas comunitárias, que são confissão, adoração, orientaçã…</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/disciplinas-comunitarias-lucas-ribas-serie-cristo-em-nos</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=17YybtA0NWs</t>
         </is>
@@ -1909,12 +1923,12 @@
           <t>…riores. Então, para isso, nós leiremos a carta de Paulo aos filipenses no capítulo 3, versículo 7, ao 14. Você pode acompanhar a sua leitura, na sua bíblia. Pensava que essas coisas eram valiosas, mas agora as consideram insignifi…</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/disciplinas-interiores-meditacao-oracao-jejum-e-estudo-lucas-gregory-serie-cristo-em-nos</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=cQ0oPF9k4pM</t>
         </is>
@@ -1956,12 +1970,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1Tm 4 (provável 1Tm 4.7-8)</t>
+          <t>1Tm 4.1-16</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1969,14 +1983,19 @@
           <t>…interiores. E eu quero iniciar, lendo o texto de primeira atimote, capítulo 4, com você pode abrir a sua bíblia na primeira carta atimote, capítulo 4. Primeiro atimote, capítulo 4, vamos ler o capítulo todo, por mais que eu…</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/podcast-12-01-25-fdqc</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=NYHFMKf0ufE</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1 Timóteo 4:1-16</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2048,12 @@
           <t>…ade. Vamos repetir? Glória Deus, nosso texto bíblico base é exo do capítulo 20, verse 1 a 3. No primeiro culto eu disse, nesse eu vou repetir, provavelmente no novo imóvel, nós não mais projetaremos o texto bíblico aqui. Pe…</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/trindade-santissima-leandro-vieira-serie-nova-era</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=kKQA8KXIFDk</t>
         </is>
@@ -2089,12 +2108,12 @@
           <t>…ra uma bíblica. Mas eu sei que você tem uma 50 em casa, né? Atos no capítulo 2, então estamos no domingo de Pentecostes. Atos capítulo 2, estarei lendo da NA, nova amea datorizada, capítulo 2, do 1 até o 13. E o texto nos di…</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/pentecostes-o-que-isso-quer-dizer-fabiano-krehnke-serie-nova-era</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=gmmLs5EjDu0</t>
         </is>
@@ -2149,12 +2168,12 @@
           <t>…rouxe, abre online mesmo, acompanhe aqui na tela. Vamos lá, atos do capítulo um. Então, hábra atos do capítulo um. Para nós fazemos a leitura bíblica dessa manhã. Atos capítulo um dos versos um ao onze, lerennos. Temos toda…</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-ascensao-de-jesus-cristo-fabiano-krehnke-serie-nova-era</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=vnnQzSiEd5Q</t>
         </is>
@@ -2196,12 +2215,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lc 24 (provável 24.36-49)</t>
+          <t>Lc 24.44-47</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -2209,14 +2228,19 @@
           <t>…. Dessa série eu gostaria que você abriu-se a sua Bíblia em Lucas, capítulo 24, do verso 44 ao 47. Essa será a nossa leitura Bíblica de hoje e a nosso ponto de partida, para a exposição que nós pretendemos desenvolver hoje. E…</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/remodelando-a-igreja-para-a-missao-felipe-bartoszewski</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Vqve13TSrUA</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Lucas 24:44-47; 2 Coríntios 5:18-20</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2293,12 @@
           <t>…s trabalhar. No primeiro culto, eu li o capítulo inteiro de Lucas, mas agora, por uma questão de tempo. Eu gostaria de que nós léssemos do verso 13 em diante, Marina, por gentileza. Nós vamos ler do 13 até 33. Tá bom? Só 20 v…</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/reajustando-a-otica-a-luz-da-ressurreicao-de-cristo-felipe-bartoszewski-serie-nova-era</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=peVCWL_1kfw</t>
         </is>
@@ -2329,12 +2353,12 @@
           <t>…orarmos ao Senhor e desenvolvermos o tema de hoje, está em João 1, capítulo 20, do verso 24 ao 28. Eu vou ler, vamos lá. Ora, Tomé, um dos 12 chamado Didmo não estava com eles quando venho Jesus, disse a ele depois, os outr…</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/podcastfinal</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=mwVVTuuKUDM</t>
         </is>
@@ -2389,12 +2413,12 @@
           <t>…ões. Nosso primeira personão é Carta de Paulo aos Ephésios, capítulo um, versículo 18 ao 21, Carta de Paulo as Ephésios, capítulo um, verso 18 ao 21. Embora sempre fazemos uso da tecnologia, não há bra mão de usar as escrituras…</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-poder-da-ressurreicao-leandro-vieira-serie-nova-era</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ldlMeQcINsE</t>
         </is>
@@ -2449,12 +2473,12 @@
           <t>…todos os que creem, digam amém. Então, o nosso texto base é Atos Capítulo 1, porque Atos é provavelmente a segunda parte de um mesmo livro escrito pelo evangelista Lucas. E fora, na organização do Canon, eles ficaram como do…</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-reino-de-deus-leandro-vieira-serie-nova-era</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=tEnRHyyiS3Q</t>
         </is>
@@ -2509,12 +2533,12 @@
           <t>…vocês só i? Abra a sua bíblia, então, na primeira carta de Pedro, no capítulo 2, eu sou um pouco mais misericordioso que eu passo toleando, que ele não projeta, eu ainda projeto ali para quem não traz sua bíblia, mas traga s…</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sacerdotes-uns-aos-outros-fabiano-krehnke-serie-reforma</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=YpznzZ9Snlk</t>
         </is>
@@ -2569,12 +2593,12 @@
           <t>…es, abra a sua bíblia. Carta de Paulo e Greja que estava em Corinto no capítulo 5, primeira aos corintios, capítulo 5, vamos ler dos versos 1 a 13. Nosso tema é disciplina na igreja. Amém? Abra a sua bíblia. Eu vou ler na ver…</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-disciplina-na-igreja-leandro-vieira-serie-reforma</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=p0t5xjGMOQI</t>
         </is>
@@ -2629,12 +2653,12 @@
           <t>…Escritura. Abra sua Bíblia. Se você tem a Bíblia física aí, salmo 119, 105, só um verso, leremos nessa manhã, salmo de número 119, o verso 105 diz, a tua palavra é lâmpada para os meus pés e luz para o meu caminho. Você pode…</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K37" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sola-scriptura-abandonada-fabiano-krehnke-serie-reforma</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=69I0KQi5Ww8</t>
         </is>
@@ -2689,12 +2713,12 @@
           <t>…sub-tema, marcas de uma igreja saudável. A Brabíblia, em 1º Timótio, capítulo 3, versículo 14 e 15. Eu disse, na semana passada, que nós, daqui para frente, vamos aos poucos parando de projetar o texto bíblico aqui. E por qu…</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/marcas-de-uma-igreja-saudavel-leandro-vieira-serie-reforma</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=umTf2qYqvoY</t>
         </is>
@@ -2749,12 +2773,12 @@
           <t>…vida. Nós vamos, então, abrir as nossas bíblias em efezios capítulo 4, verso 1 e 2, o texto que vai ser hoje a nossa leitura bíblica, a nossa base de reflexão, para que nós possamos expor as escrituras, a luz do Evangelho de ac…</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/servir-felipe-bartoszewski-serie-verbos-cristaos</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Wa5EhJde_aI</t>
         </is>
@@ -2809,12 +2833,12 @@
           <t>…ura, evangelica e evangelística de evangelização. Vamos ler romanos, capítulo 1, o versículo 16 e 17. Então nós vamos ler romanos 1, depois nós pulamos para marcos 16, se você quiser, tem um marcador na sua página, na sua bíbli…</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/evangelizar</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L40" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=fkqyvgM6Eck</t>
         </is>
@@ -2869,12 +2893,12 @@
           <t>…que assumimos em comunidade. O nosso texto base em segunda corinte, o capítulo 8, é um texto extensivo, peço que você preste muita atenção. Eu tibiai algumas vezes por saber que são muitos versículos, mas aí o espírito me le…</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/contribuir-leandro-vieira-serie-verbos-cristaos</t>
         </is>
       </c>
-      <c r="L41" s="2" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=5EDU6rtYz8M</t>
         </is>
@@ -2929,12 +2953,12 @@
           <t>…e de autoridade, nós vamos olhar para o texto de Matheus, o capítulo 8, versículo 5, ao 10, que aí não tem a escritura, acompanha aqui. Vamos lá, entretanto Jesus em Carfanaum dirigiu-se a Ele um centurão pedindo, ele ajuda. Edi…</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/honrar-leandro-alves-serie-verbos-cristaos</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=D7cNHTR7Xio</t>
         </is>
@@ -2989,12 +3013,12 @@
           <t>…mos trabalhar essas verdades de nosso texto base de hoje, é Ebreus, capítulo 10, versus 19 a 25. Vamos orar. Parte de damos graças, uma vez mais. Reguemos o nome de Cristo Jesus, mas alto do que qualquer outro nome. E nós, rog…</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/congregar-leandro-vieira-serie-verbos-cristaos</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=RMV-PQ4BxJY</t>
         </is>
@@ -3049,12 +3073,12 @@
           <t>…ito importante nós termos a nossa Bíblica, abra aí então em Mateus, evangelho de Mateus, no capítulo de número 28, Mateus 28, vamos ler os versículos 18 a 20, texto bastante conhecido, texto da grande comissão, desse grande en…</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/discipular-fabiano-krehnke-serie-verbos-cristaos</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=5PLY3tG-WoA</t>
         </is>
@@ -3109,12 +3133,12 @@
           <t>…bém de sermos um testemunho ao mundo. Testo bíblico nosso é Salmos, capítulo 95, verso 1 a 6. Vamos ler a palavra de Deus. Venham, cantemos ao Senhor conjúbelo, celebramos o rochedo da nossa salvação, saíamos aos seus encontr…</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K45" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/cultuar-leandro-vieira-serie-verbos-cristaos</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=TZwsRqZvshw</t>
         </is>
@@ -3169,12 +3193,12 @@
           <t>…ãos para abrir em a Bíblia na Cáetria de Paulo dos Humanos, Capítulo 12, quanto vocês abrem, eu vou fazendo a introdução. Hoje nós estaremos dando continuidade encerrando a nossa série sobre disciplinas espirituais, mas não apen…</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/disciplina-do-servico-lucas-gregory-serie-fome-por-deus</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=QKHYNGemZvA</t>
         </is>
@@ -3229,12 +3253,12 @@
           <t>…us. O texto, basicamente, que a gente utiliza, vai utilizar ebreus 10, 19, 25, e nós vamos ler o texto, seguir dourámos e descorremos a respeito do sermão. Vamos juntos, então, ebreus 10, 19, 25, a versão NAA, que diz. Portant…</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/disciplina-da-comunhao-felipe-garrote-serie-fome-por-deus</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Un-MAGYgi4E</t>
         </is>
@@ -3289,12 +3313,12 @@
           <t>…o texto que nós vamos estudar juntos hoje aqui é o texto de Salmos 19, mais específico os versículos do Sétil e ao 14. Porém, nós vamos ler primeiro juntos, todos salmos, já que não são tantos versículos, para que a gente com…</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/escrituras-e-oracao-lucas-ribas-serie-fome-por-deus</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L48" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=1jy0oU-4Q7Q</t>
         </is>
@@ -3349,12 +3373,12 @@
           <t>…o crescimento, no conhecimento do Senhor. A gente vai ler o Salmo 63 agora, ele vai ser a base da nossa pregação de hoje, nossa irmão. Ele diz assim, a minha alma tem cedite, a minha carne deseja muito em uma terra seca e can…</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K49" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/fome-por-deus-felipe-bartoszewski-serie-fome-por-deus</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=3354MZ8EBJE</t>
         </is>
@@ -3401,7 +3425,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -3409,14 +3433,19 @@
           <t>…onte, o Injeiro Zalém. E ele responde da seguinte forma, um versículo muito famoso que todos vocês conhecem, em juão, quatro, vinte e três diz que os verdadeiros adoradores, adorarão ao pai em espírito e em? E são estes que o pai…</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K50" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/devocao-e-oracao-jaqueline-krehnke-serie-oracao</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=oKd30s9ecLo</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>João 4:23-24; Deuteronômio 6:5</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3485,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Mt 6.5ss</t>
+          <t>Mt 6.5-13</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -3469,14 +3498,19 @@
           <t>…ar com um versículo muito conhecido por nós, que está lá em Mateus, capítulo 6, verso 5, tá? Mateus 6, verso 5, mas eu não vou começar com todo o versículo. Eu vou começar com apenas três palavras desse versículo que se encont…</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/praticando-a-oracao-leivison-rosa-serie-oracao</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=YLGgZ2k47xU</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Mateus 6:5-13; Gênesis 1:26</t>
         </is>
       </c>
     </row>
@@ -3529,12 +3563,12 @@
           <t>…seja uma verdade a nossa vida. Vamos abrir as escrituras no salmo, capítulo 1 por gente lhesa. Eu vou ler na versão ACF, é o meio da corrida fiel, que diz assim. Bem-aventurado, homem que não anda segundo o Conselho dos Ímpio…</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/aprofundando-a-oracao-felipe-bartoszewski-serie-oracao</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-X6DfAgbTXM</t>
         </is>
@@ -3589,12 +3623,12 @@
           <t>…ender com Jesus como orarmos. A oração do Pai Nosso está em Mateus, no capítulo 6, versículos 5 ao 13, vocês orem assim, Pai Nosso que está nos céus santificados seja o seu nome. Venha o teu reino, seja feita a tua vontade, as…</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/aprendendo-a-orar-lucas-gregory-serie-oracao</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="L53" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=c1VCBjFFrgo</t>
         </is>
@@ -3649,12 +3683,12 @@
           <t>…e algumas inserções dele aqui. Então, vamos para o texto de João. A gente vai falar sobre compreender a oração. E vamos ler o texto de João, capitulo 17, versículo 13 até o versículo 24. Eu estou usando a versão nova, a hume…</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K54" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/compreendendo-a-oracao-fabio-fontoura-serie-oracao</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="L54" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ZiZuGmZAWCw</t>
         </is>
@@ -3709,12 +3743,12 @@
           <t>…ia que você, desde logo já abri-se a sua Bíblia, o livro de Salmos, capítulo 109. Nós vamos ler o versículo 4. Salmos 109 e 4. Nós estamos utilizando, indicando como literatura para essa série, o livro oração do Timoth Keller…</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/desejando-a-oracao-juliano-marold-serie-oracao</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="L55" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=d8x1cQTy3Zw</t>
         </is>
@@ -3769,12 +3803,12 @@
           <t>…aciência comigo. Vamos ler o capítulo é a primeira carta de João no capítulo 4, versículo 7. Acompõe aqui comigo. Desacim. Amados, amemos uns aos outros, pois o amor procede de Deus, aquele que ama nascido de Deus e conhece…</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-amor-na-trindade-leandro-alves-serie-trindade</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="L56" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=oMxY2N0tWfY</t>
         </is>
@@ -3829,12 +3863,12 @@
           <t>…resente, é só para você colocar ali do lado. Glória a Deus, efésios capítulo 1, por favor. O nosso texto básico para a exposição vai do verso 3 ao 14 de efésios. Bendito, o Deus e pai, diga, Deus e pai, de nossos senhores Jesus…</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K57" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-trindade-e-a-adoracao-leandro-vieira-serie-trindade</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="L57" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=raf3tM8HrBM</t>
         </is>
@@ -3876,12 +3910,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Jo 17 (oração sacerdotal)</t>
+          <t>Jo 17.17-26</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
@@ -3889,14 +3923,19 @@
           <t>…amém para a oração do seu filho Jesus Cristo relatada quem João Cabeito 17. O nosso desejo aqui possamos ser o comprimento daquilo que ele pediu para o Senhor. Nós sabemos que já temos sido esse comprimento parcial e nós pe…</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K58" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-unidade-da-trindade-felipe-bartozewski</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="L58" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=wm9-B4fmkLA</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>João 17:17-26</t>
         </is>
       </c>
     </row>
@@ -3949,12 +3988,12 @@
           <t>…, filho e espírito. Então a nossa leitura é no Evangelho de Marcos, a leitura bíblica dessa manhã, a palavra do senhor de Evangelho de Marcos, no primeiro capítulo, os versículos 9 até 11, nós vamos ler nessa manhã. Então, mar…</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K59" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/unidade-adoracao-e-amor-fabiano-krehnke-serie-trindade</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="L59" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=5LxBRE9R_Rk</t>
         </is>
@@ -4001,7 +4040,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -4009,14 +4048,19 @@
           <t>…o texto gostaria que você olhasse, e a notasse, é, primeiro Corinthians 10, 31, onde está escrito. Portanto, seja comendo, seja bebendo, seja fazendo qualquer outra coisa, fazer tudo para glória de Deus. Amém? Então veja, tod…</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K60" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-e-o-trabalho-um-novo-enredo-conceito-direcao-e-motivacao-leandro-alvesfe-trabalho</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="L60" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=9H3opnlI7zc</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>1 Coríntios 10:31; Tiago 1:17</t>
         </is>
       </c>
     </row>
@@ -4069,12 +4113,12 @@
           <t>…tema da nossa palavra. E a nossa leitura bíblica da manhã é Gênesis, capital 11. Então se você tem a sua bíblica deseja abril a abren Gênesis 11, 2 a 4 agora. Os homens deslocaram-se para o Oriente e acharam um vale na Terra de…</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/egoismo-e-idolatria-no-trabalho-fabiano-krehnke-serie-fe-trabalho</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=0HuwE5iSjYE</t>
         </is>
@@ -4129,12 +4173,12 @@
           <t>…s faremos nessa manhã antes de entrarmos nesse tema está em gênesis no capítulo 3 do versículo 16 até 2019, então você pode abrir a sua bíblica ou acompanhar na tela na projeção, que também será projetado. Então, gênesis 3 e de…</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/trabalho-infrutifero-e-sem-sentido-fabiano-krehnke-serie-fe-trabalho</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=uzksse2dAow</t>
         </is>
@@ -4189,12 +4233,12 @@
           <t>…e servir ao Senhor e servir ao próximo. O nosso texto base, Genesis 1, 28, a Escritura diz, Deus usa o abençoou, ele diz se sejam férteis e multipliquem-se, enxam e subjugen a terra. Com o seu cabeça, quero orar pai, te damos g…</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K63" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/trabalho-dignidade-cultivo-e-servico-leandro-vieira-serie-fe-trabalho</t>
         </is>
       </c>
-      <c r="L63" s="2" t="inlineStr">
+      <c r="L63" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=gYqfRg5Ajiw</t>
         </is>
@@ -4236,12 +4280,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Gn 1.31; 2.15</t>
+          <t>Gn 1.31–2.3; 2.15</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
@@ -4249,14 +4293,19 @@
           <t>…alho, já já. Eu trago justificativas, Géneas escapito no I, versículo 31, e iremos a Géneas II, I II e I III, I. Vérsso XV, o texto inicial para a nossa reflexão e início dessa nova série. Ok? E viu Deus tudo quanto tinha feito e…</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K64" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/trabalho-vocacao-ou-punicao-leandro-vieira-serie-fe-trabalho</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L64" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=AVLprNam4NI</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Gênesis 2:1-3, 15; Efésios 4:28; 1 Coríntios 15:58; 2 Coríntios 5:10</t>
         </is>
       </c>
     </row>
@@ -4309,12 +4358,12 @@
           <t>…es dele subir aos céus através da ascensão. Então vamos ler Mateus, capítulo 28, eu voleiro um ou 8 e depois eu vou pular lá para o 17 perdão, ai eu vou pular lá para o 16 e voleiro até o 20. Vamos lá. E no fim do sábado, quan…</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="K65" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-ressurreicao-de-jesus-felipe-bartoszewski-serie-ele-veio-para-servir</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="L65" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Nf1pl4Lte1A</t>
         </is>
@@ -4369,12 +4418,12 @@
           <t>…i relatar esta manhã tão especial que nós vemos relatado em João. Então, João Capítulo 20, se você quiser abrir, o tema da nossa mensagem nessa manhã é a realidade da ressurrição. Então, nós falaremos sobre o quão real a res…</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-realidade-da-ressurreicao-fabiano-krehnke-serie-ele-veio-para-servir</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="L66" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ROFKYWPEgUA</t>
         </is>
@@ -4429,12 +4478,12 @@
           <t>…alma, é salvação para nossa alma. Nosso texto bíblico hoje, Marcos Capítulo 11, versículo 1 a 26, quando tudo nós vamos ler em três porções, a primeira vai de 1 a 11, ok? É justamente o texto que registra esse domingo de ramos…</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="K67" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-entrada-triunfal-leandro-vieira-serie-ele-veio-para-servir</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="L67" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=oQ2p6tvNJwk</t>
         </is>
@@ -4489,12 +4538,12 @@
           <t>…os. A sua ordem de culto tem a leitura bíblica de primeira, Pedro 2, 21 a 25, mas eu decidi antecipar alguns versículos, ler alguns versículos antes, então nós vamos começar do 11, do 11, iniciaremos. Para ter um pouco mais d…</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="K68" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/reverente-submissao-fabiano-krehnke-serie-ele-veio-para-servir</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=diTaIHcj7eQ</t>
         </is>
@@ -4549,12 +4598,12 @@
           <t>…istério Cristão. Então o nosso texto base, ele será segundo Corinthians, capítulo 5, versículo 15, onde está escrito assim e ele morreu por todos para que aqueles que vivem já não vivam mais para si mesmos, mas para aquele qu…</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="K69" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-e-o-ministerio-cristao-leandro-alves-serie-ele-veio-para-servir</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="L69" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=pbcOp_JidDE</t>
         </is>
@@ -4596,12 +4645,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fp 2.3</t>
+          <t>Mc 10.35-45? / Fp 2.3</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Incerto — revisar (fontes divergem)</t>
         </is>
       </c>
       <c r="J70" s="4" t="inlineStr">
@@ -4609,14 +4658,19 @@
           <t>…ão, o que é o ativismo religioso? Paulo, em Felipe Ensemos, capítulo 2, verse 3 ele diz assim, e nada façá-se por partidarismo ou vanguola, ele está falando isso no âmbito da igreja local. E esteço dá a entender, ele abre a poss…</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="K70" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-problema-do-ativismo-religioso-felipe-bartoszewski-serie-ele-veio-para-servir</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="L70" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-s1dNx1cKZk</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2 Coríntios 11; Marcos 10:35-45</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4710,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Jo 13–17</t>
+          <t>Mc 10.35-45; Jo 13</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4669,14 +4723,19 @@
           <t>…o pão, abençoando o cálice, como o símbolo da nova aliança. João do capítulo 13 ao 17, ele trata do ensinamento de Cristo e há algo que é central no ensinamento de Cristo porque, em João capítulo 13, Cristo, ele vestisse com…</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="K71" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-ceia-e-o-ministerio-cristao-leandro-vieira-serie-ele-veio-para-servir</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="L71" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=u6ptVq_iW0Y</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Marcos 10:35-45; João 13; Filipenses 2:5-11; 1 Pedro 4:7-11</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4788,12 @@
           <t>…ã será apenas desse versículo 16 do capítulo 10 de primeira corintio, por conta de os 10, 16. Tesso diz o seguinte, não é fato que o cálice da benção que abençoamos é a comunhão do sangue de Cristo, e não é fato que o pão que…</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="K72" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/meio-de-graca-fabiano-krehnke-serie-celebracao-da-redencao</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="L72" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=dP7JH7zqUXk</t>
         </is>
@@ -4789,12 +4848,12 @@
           <t>…vão registrar a última seia, Paulo escreve primeiramente a Corinthians. Paulo não recebeu isso de nenhum apostro, inclusive, no versículo 23, ele dizá o que poderia suar até meio assim, metido a parte do Paulo, né? O Paulo d…</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="K73" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/discernindo-o-corpo-de-cristo-leandro-vieira-serie-celebracao-da-redencao</t>
         </is>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="L73" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=xF5UI7efMJM</t>
         </is>
@@ -4849,12 +4908,12 @@
           <t>…então a gente está seguro para fazer essa transição, vamos amarcos capítulo 14 versículo 22 a 26, e enquanto comem, tomou Jesus um pão, do Lorde, Deus, manhã eu tenho que cortar, eu pedi para o cara abrir o cara abrir, mas não…</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K74" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-mesa-do-senhor-leandro-vieira-serie-celebracao-da-redencao</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="L74" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Y7G1cPncq0M</t>
         </is>
@@ -4909,12 +4968,12 @@
           <t>…pela celebração, pela orientação, o primeiro texto está em Colossenses, capítulo 3, versículo 16. Eu acho que vai estar aqui atrás. Colossenses 3, 16. A escritura diz assim que a palavra de Cristo habite ricamente em vocês. Estrua…</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K75" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/orientacao-e-celebracao-juliano-marold-serie-disciplina-e-liberdade</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="L75" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=dXVwnElKrN8</t>
         </is>
@@ -4956,12 +5015,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Mc 1.35</t>
+          <t>Mc 1.35? / Lc 18.15-17</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Incerto — revisar (fontes divergem)</t>
         </is>
       </c>
       <c r="J76" s="4" t="inlineStr">
@@ -4969,14 +5028,19 @@
           <t>…todos, por que a gente não consegue se organizar? Vamos lá. Marcos 1, 35 diz assim, de madrugada, em meio à escuridão Jesus levantou-se, saiu da casa e retirou-se para um lugar deserto onde ficou orando, o que nos falta é a pr…</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/solitude-e-comunhao-lucas-balzer-serie-disciplina-e-liberdade</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=qcXMx5LJq14</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Lucas 18:15-17; Romanos 12:9-12; 1 Coríntios 11</t>
         </is>
       </c>
     </row>
@@ -5029,12 +5093,12 @@
           <t>…esus, seja verdade na nossa vida. Abre comigo a sua bíblia, Mateus, capítulo 6. A gente vai ler do 5 ao 18. Eu vou ler aqui na CF, desasim. E quando horários não seja como os hipócritas, pois se comprasem em horar, em pé nas s…</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K77" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/oracao-e-jejum-felipe-bartoszewski-serie-disciplina-e-liberdade</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="L77" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=QUjzS6D888c</t>
         </is>
@@ -5089,12 +5153,12 @@
           <t>…estudo. Então, o texto base dessa ministração é, segundo a Pedro 3, 18, que vai dizer, cresçam porém na graça e no conhecimento de nosso Senhor e Salvador Jesus Cristo. Aí, ele seja aglória, agora e para sempre. Amém! Então,…</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="K78" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/meditacao-e-estudo-lucas-gregory-serie-disciplina-e-liberdade</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="L78" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7f6nfpXBa8</t>
         </is>
@@ -5141,7 +5205,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -5149,14 +5213,19 @@
           <t>…ais para a gente. Então, vamos começar com o Felipe Penses, capítulo 1, é pistola de Paulo aos Felipe Penses nos ajuda a começar a pensar um pouco nesse caminho e a gente vai olhar para algumas passagens, a gente vai pedir para…</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="K79" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-cidade-de-deus-e-a-cidade-dos-homens-yago-martins-serie-cristao-e-cultura</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="L79" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=syGnxMAzPAQ</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Filipenses 1:27-30; Hebreus 12:26-28; 1 Pedro 2:11-15</t>
         </is>
       </c>
     </row>
@@ -5209,12 +5278,12 @@
           <t>…mundo cristã, numa sociedade não cristã. Nosso texto base é João, capítulo 17, se você tem a inscritura, tome ela, por favor. Oração sacerdotal do Senhor, nós já utilizamos um texto de João capítulo 17, na minha penúltima me…</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="K80" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-mente-crista-leandro-vieira-serie-cristao-e-cultura-1</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="L80" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=217K_NUzPlM</t>
         </is>
@@ -5269,12 +5338,12 @@
           <t>…es. Para isso eu gostaria que você abrisse as escrituras em Mateus, capítulo 22. Eu esqueci de passar o texto bíblico, por time lá. Vamos ler do versículo 15 em diante. Mateus, capítulo 22, verso 15. Então, retirando seus fari…</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="K81" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-cristao-e-a-politica-leandro-vieira-serie-cristao-e-cultura</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="L81" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=61PDyIPnzmQ</t>
         </is>
@@ -5325,12 +5394,12 @@
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr"/>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K82" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-formacao-da-cultura-felipe-bartoszewski-seriecristao-e-a-cultura</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="L82" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=WHtgPU8r3F4</t>
         </is>
@@ -5385,12 +5454,12 @@
           <t>…m as coisas criadas. O texto base para essa ministração é o Romanos I do 1823. A ira de Deus se revela do céu contra toda a impiedade e a injustiça dos seres humanos, que, por meio da sua injustiça, suprime a verdade, pois o qu…</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K83" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/receber-rejeitar-e-redimir-a-cultura-lucas-gregory-serie-cristao-e-a-cultura</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="L83" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=kbPSFbs1L5U</t>
         </is>
@@ -5445,12 +5514,12 @@
           <t>…m tudo que vamos compartilhar. Capítulo 17, do Evangelho de João, o versículo 15, especialmente. Capítulo 17, versículo 15. Não peço que o estílio do mundo e sim que os guardes do mal. Curva sua cabeça, pai. Tidamos graças u…</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="K84" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-igreja-e-a-crise-cultural-leandro-vieira-serie-cristao-e-cultura</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="L84" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=1v1bFGLIo2k</t>
         </is>
@@ -5505,12 +5574,12 @@
           <t>…a de hoje é o mandato cultural. Nós vamos ler juntos agora, gênesis 2.15, então abra sua biblinha gênesis 2.15. É um versículo só mesmo, abre gênesis 2.15 e deixa aí o seu marcadorzinho, seu d, da alguma coisa, quando se achou…</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K85" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/mandato-cultural-fabiano-krehnke-serie-cristao-e-a-cultura</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="L85" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=a-i68iFDSj8</t>
         </is>
@@ -5565,12 +5634,12 @@
           <t>…cultura. Redenção nas relações. Vamos abrir as criaturas em atos capítulo 17. Vamos ler do verso 15 ao verso 22. A escritura de Zascendius, que acompanhava um Paulo, levaram até atenas, e recebendo ordem para que Silas e Tim…</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="K86" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/ideologia-a-religiao-secular-leandro-vieira-serie-cristao-e-a-cultura</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="L86" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=0HxZGKtOx4A</t>
         </is>
@@ -5625,12 +5694,12 @@
           <t>…s bárbaros, vamos projetar lá. Abra a escritura em primeira corintos, capítulo 14, por favor, nós vamos usar esse texto como nossa base para a reflexão agora aqui, primeira corintos, capítulo 14, antes, deixe aí eu justificar…</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="K87" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/cativeiro-ideologico-leandro-vieira-serie-cristao-e-a-cultura</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="L87" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=AwTI5XXQrgg</t>
         </is>
@@ -5672,12 +5741,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>At 17</t>
+          <t>At 17.16-34</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -5685,14 +5754,19 @@
           <t>…a ordem de nós nos relacionarmos com as coisas criadas vem gênesis 1 e 2, ou seja, antes de gênesis 3, antes da queda. Isso determina que as nossas relações com a cultura, o nosso mandato cultural não é, ou o trabalho, e se não…</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="K88" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-exegese-cultural-fabiano-krehnke-serie-cristao-e-a-cultura</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="L88" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=b6Jv0UZhf-Y</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Atos 17:16-34</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5819,12 @@
           <t>…u quiser acompanhar aqui também, fica a vontade. Abra lá em João, o Evangelho de João, capítulo 20, versículo 20 a 23. João, 20 a 23. Então, vamos dizer assim, deixa eu olhar aqui pra ficar. E dizendo isso, mostrou-lhe a sua…</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K89" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/confissao-adoracao-e-celebracao-juliano-marold-serie-disciplinas-espirituais</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="L89" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=qVVkOQe7sNo</t>
         </is>
@@ -5796,12 +5870,12 @@
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr"/>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="K90" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/solitude-silencia-e-descanso-lucas-balzer-serie-disciplinas-espirituais</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="L90" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Q5zmc3JXw8E</t>
         </is>
@@ -5856,12 +5930,12 @@
           <t>…exto que nós vamos começar, além do nesta manhã, está lá em Mateus, capítulo 6, versículo 19. Eu vou ler aqui, deixa eu ver se está igual, não está igual, eu vou ler junto com vocês. Não ajunteis para vos tesouros na Terra ond…</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K91" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/simplicidade-submissao-e-servico-willian-amaral-serie-disciplinas-espirituais</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr">
+      <c r="L91" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=bowcMKrPcZ4</t>
         </is>
@@ -5916,12 +5990,12 @@
           <t>…r um texto com vocês que está em segunda pedra, o segundo é Pedro, o 1, verso 3 até o 11. Visto como seu divino poder nos deu tudo o que diz respeito à vida e à piedade, pelo conhecimento daquele que nos chamou para a sua gló…</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="K92" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/oracao-meditacao-e-jejum-felipe-bartoszewski-serie-disciplinas-espirituais</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr">
+      <c r="L92" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=WeTUwESgqHc</t>
         </is>
@@ -5976,12 +6050,12 @@
           <t>…timo livro das escrituras não atou a chamada de revelação e apocalipse capítulo 1, versículo 1, a primeira parte do versículo diz, esta é a revelação de Jesus Cristo. Então embora o livro vai tratar de orientações que Jesus dá à sua igreja…</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="K93" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-cristo-eterno-leandro-vieira-serie-advento</t>
         </is>
       </c>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="L93" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=AkKpRC4Jj6Y</t>
         </is>
@@ -6036,12 +6110,12 @@
           <t>…isto. Eu gostaria que você leste comigo o texto de primeira João no capítulo 2 do 28 até o 3.3. Então, vamos pegar a aliaça a transição entre os dois capítulos do 28, capítulo 2, 28 até o 3.3, que é um dos muitos textos esca…</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="K94" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-advento-futuro-fabiano-krehnke-serie-advento</t>
         </is>
       </c>
-      <c r="L94" s="2" t="inlineStr">
+      <c r="L94" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Za9TbSXSsIc</t>
         </is>
@@ -6083,12 +6157,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2Co 4.6?</t>
+          <t>Cl 1.26-29</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Incerto — revisar</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -6096,14 +6170,19 @@
           <t>…tão falando de uma condição. Lembra quando Paulo escreve os romanos, 3, 23, ele diz todos pecaram, quem lembra? E destituídos foram da glória de Deus, ou seja, nós perdemos a glória. Que glória? Aquela glória original que o homem…</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K95" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-rei-entre-nos-leandro-vieira-serie-advento</t>
         </is>
       </c>
-      <c r="L95" s="2" t="inlineStr">
+      <c r="L95" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=TcWCepTCCuc</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Colossenses 1:26-29; Efésios 1:21-23; Mateus 28:18-20</t>
         </is>
       </c>
     </row>
@@ -6156,12 +6235,12 @@
           <t>…uestão da divindade e da humanidade de Jesus. Esse texto de João 1, ele não é um texto novo. Quem aqui já ouviu esse texto? Todos nós. É um dos textos mais conhecidos. O evangelho de João é a porção das escrituras mais publi…</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="K96" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-deus-que-se-fez-homem-felipe-bartoszewski-serie-advento</t>
         </is>
       </c>
-      <c r="L96" s="2" t="inlineStr">
+      <c r="L96" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=e8c-71NajvQ</t>
         </is>
@@ -6216,12 +6295,12 @@
           <t>…qui. Então, eu lentei comigo aí o texto de segunda pedra no capítulo 1, do versículo 12, até o 21. Vou ler aqui, você acompanha aí. Por essa razão, sempre estarei pronto para trazer-vos lembrados acerca destas coisas. Embora est…</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="K97" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/introducao-ao-calendario-cristao-fabiano-krehnke-serie-advento</t>
         </is>
       </c>
-      <c r="L97" s="2" t="inlineStr">
+      <c r="L97" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=BWhNLXE3Ne0</t>
         </is>
@@ -6263,12 +6342,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Gálatas (ênfase Gl 5)</t>
+          <t>Gl 5.1-13</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -6276,14 +6355,19 @@
           <t>…ara treinar na internet nome de Jesus amém, estamos juntos. Galatas capítulo 5 é um texto que ele vai resumir a mensagem de Galatas, porque o verso 1, Paulo, perdão, o verso 4, ele vai dizer que aquele que busca a justificação para as o…</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="K98" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/distorcoes-sobre-a-graca-felipe-bartoszewski-serie-graca-sobre-graca</t>
         </is>
       </c>
-      <c r="L98" s="2" t="inlineStr">
+      <c r="L98" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7u5jfjSTMG0</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Gálatas 5:1-13; Marcos 1:14-15; Romanos 2:4</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6407,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Ef 2.10</t>
+          <t>Ef 2.10; Fp 2.12-13</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -6336,14 +6420,19 @@
           <t>…sobre a realidade do que vamos falar nessa manhã. Efeitos, capítulo dois, versículo dez, nos diz assim, pois somos feitura dele criados em Cristo Jesus para boas obras, as quais Deus, de antemão, preparou para que andásemos nel…</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K99" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/os-meios-de-graca-fabiano-krehnke-serie-graca-sobre-graca</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="L99" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=GIrDbQPIXBg</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Efésios 2:10; Filipenses 2:12-13; 2 Pedro 3:18; 2 Timóteo 3:16-17</t>
         </is>
       </c>
     </row>
@@ -6396,12 +6485,12 @@
           <t>…a isso eu gostaria de abrir com vocês o texto de, segundo a Reis, capítulo 22, vai ser o nosso texto base para a nossa reflexão e eu vou engrossar o cao do hoje, amém? Então, provavelmente você vai precisar escutar essa mens…</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K100" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-reforma-e-o-evangelho-da-graca-leandro-vieira-serie-graca-sobre-graca</t>
         </is>
       </c>
-      <c r="L100" s="2" t="inlineStr">
+      <c r="L100" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=d3b_8Yunl_I</t>
         </is>
@@ -6456,12 +6545,12 @@
           <t>…iniciar fazendo a leitura do texto bíblico de Evangélia de João, capítulo 1, versículo 12 e 13. Conhecido o texto das escrituras, nos diz o seguinte, mas a todos quantos o receberam, deu o Lisbo poder de serem feitos, leu c…</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K101" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20211024-leandro-vieira-audio</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr">
+      <c r="L101" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7kg72fMixww</t>
         </is>
@@ -6516,12 +6605,12 @@
           <t>…staria que você fiz essa leitura comigo do texto Bíblico de Tiago 1 do versículo 16 ao versículo 18. E eu gostaria de convidar você a ficar de pé para essa leitura Bíblico, eu gostaria de fazer isso. Se a gente estava numa ig…</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="K102" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-graca-comum-e-diaria-fabiano-krehnke-serie-graca-sobre-graca</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr">
+      <c r="L102" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=pdivB31Ta5o</t>
         </is>
@@ -6576,12 +6665,12 @@
           <t>…m, gente? Então, eu gostaria que abrísemos as escrituras em Filipenses, capítulo 3. Os versos dezoito e dezenove. E, pois muitos andam entre nós, dos quais repetidas vezes eu vos dizia e agora, vos digo, até chorando que são inimi…</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K103" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-idolo-nao-e-nada-leandro-vieira-serie-a-fabrica-de-idolos</t>
         </is>
       </c>
-      <c r="L103" s="2" t="inlineStr">
+      <c r="L103" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=2VBDaK26K8I</t>
         </is>
@@ -6636,12 +6725,12 @@
           <t>…sposta, sempre estar atenta isso, também? Vamos ver, então, Jonas, está projetado ali? Capítulo 2, do verso 2.9, diz o seguinte, uma oração de Jonas ao Senhor, ok? E disse, clamei ao Senhor na minha aficção e ele me ouviu, do…</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
+      <c r="K104" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/iddentificando-idolos-culturais-willian-amaral-serie-a-fabrica-de-idolos</t>
         </is>
       </c>
-      <c r="L104" s="2" t="inlineStr">
+      <c r="L104" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=FlR1WAe5vN0</t>
         </is>
@@ -6696,12 +6785,12 @@
           <t>…mínimo que deu para pegar aqui sobre isso. Vamos ler juntos Daniel no capítulo 4, abra sua bíblica se você tem ela. Nós vamos ler aqui na versão revista atualizada, a real, o meio da revista atualizada, o capítulo 4. Primeiro…</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="K105" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/poder-gloria-fabiano-krehnke-serie-a-fabrica-de-idolos</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr">
+      <c r="L105" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-9Nzt5s5ArI</t>
         </is>
@@ -6756,12 +6845,12 @@
           <t>…e a palavra chave que eu vou trazer aqui, está em marco do capítulo 8, no verso 34 e verso 35, eu gostaria que você me acompanhasse na leitura. Verso 34 diz assim, então ele chamou a multidão e os discípulos e disse, se alguém…</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="K106" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/alves-1</t>
         </is>
       </c>
-      <c r="L106" s="2" t="inlineStr">
+      <c r="L106" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=KSYqJBGoIDM</t>
         </is>
@@ -6816,12 +6905,12 @@
           <t>…ganância, eu gostaria que você abriça sua bíblia comigo? Em Lucas, capítulo 12, 15, nós vamos ver até o 31. Então, ele recomendou, tem de cuidar e guardar ivos de toda e qualquer avareza, porque a vida de um homem não consist…</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="K107" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/dinheiro-ganancia-felipe-bartoszweski-serie-a-fabrica-de-idolos</t>
         </is>
       </c>
-      <c r="L107" s="2" t="inlineStr">
+      <c r="L107" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=x7PuqOmUdFo</t>
         </is>
@@ -6876,12 +6965,12 @@
           <t>…oje sobre como nós criamos um ídolo. E o texto base está em romanos 1,21 a 25. Vamos lá. Versículo 21 diz assim. Por quanto tendo conhecimento de Deus, não glorificaram como Deus. Nem lideram graças. Antes, se tornaram nulos em…</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="K108" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/como-criamos-um-deus-jaqueline-krehnke-serie-a-fabrica-de-idolos</t>
         </is>
       </c>
-      <c r="L108" s="2" t="inlineStr">
+      <c r="L108" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=iVLlboM58u0</t>
         </is>
@@ -6936,12 +7025,12 @@
           <t>…E para começar, eu gostaria de nós lermos juntos o texto de Ebreus 10, 19, 25, foi um texto que eu separei para que nós possamos fazer a nossa leitura bíblica de hoje, que tem a ver que é totalmente conectado com o que nós vam…</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="K109" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-culto-encenacao-da-redencao-fabiano-krehnke-minisserie-igreja-o-evangelho-visivel</t>
         </is>
       </c>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="L109" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=MqhTVz3RkS8</t>
         </is>
@@ -6983,12 +7072,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Mt 16.18; 18.15-20</t>
+          <t>Mt 18.15-20</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J110" s="4" t="inlineStr">
@@ -6996,14 +7085,19 @@
           <t>…vez que Cristo mencione a igreja. A primeira mensão está no capítulo 16 e no capítulo 18, o Senhor destruindo aos seus discípulos diz, ó, se tem um irmão pecar contra ti, vai e repreendio entre ti e ele só. Se te ouvir, ganhaste…</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="K110" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-autoridade-e-a-missao-central-da-igreja-leandro-vieira-minisserie-igreja-o-evangelho-visivel</t>
         </is>
       </c>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="L110" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jEa3UoLG4hw</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Mateus 18:15-20</t>
         </is>
       </c>
     </row>
@@ -7056,12 +7150,12 @@
           <t>…edade das palavras que Paulo usa na introdução da carta aos galatas quando de Galatas capítulo 1, verso 6 ao 9, ele diz que se ele ou qualquer outro, ainda um anjo do céu anunciasse outro Evangelho, além daquele que ele já havia anunciado, que fosse mald…</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr">
+      <c r="K111" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-que-e-uma-igreja-parte-2-leandro-vieira-minisserie-igreja-o-evangelho-visivel</t>
         </is>
       </c>
-      <c r="L111" s="2" t="inlineStr">
+      <c r="L111" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=4QJBNPKShtM</t>
         </is>
@@ -7116,12 +7210,12 @@
           <t>…Paulo já falou a respeito da graça salvífica, nos primeiros capítulos, ele fala em várias cartas a respeito da graça pedagógica, que nos ensina a viver com o matido, mas ele está falando do aspecto vocacional da graça com uma ca…</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K112" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-que-e-uma-igreja-parte-2-leandro-vieira-minisserie-igreja-o-evangelho-visivel</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="L112" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=W3boBT1SZv0</t>
         </is>
@@ -7176,12 +7270,12 @@
           <t>…r um nível na nossa compreensão de igreja. Então, primeira atimote o capítulo 3, versículo 14, em diante. Na verdade, hoje, essa primeira mensagem da série vai servir como um fechamento da última série, efejos pensando falan…</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="K113" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-nova-sociedade-leandro-vieria-minisserie-igreja-o-evangelho-visivel</t>
         </is>
       </c>
-      <c r="L113" s="2" t="inlineStr">
+      <c r="L113" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=gUR8GAhxfzs</t>
         </is>
@@ -7236,12 +7330,12 @@
           <t>…nós vamos colocar em sequência aqui, começando por John no capítulo 37, no versículo 23, por favor. Quanto ao Todo-Poderoso, não podemos compreender grande empoderes justiça e pleno derretidão a ninguém poes, ou primirá. Próxim…</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
+      <c r="K114" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-onipotencia-de-deus-leandro-alves-serie-atributos-divinos</t>
         </is>
       </c>
-      <c r="L114" s="2" t="inlineStr">
+      <c r="L114" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=r56eaVrB4W4</t>
         </is>
@@ -7291,12 +7385,12 @@
           <t>…aturas. Amém? Eu achei essa mensão sensacional, ela fecha o capítulo de sabedoria do livro do Tozer, e eu só quero relembrar o motivo pelo qual nós estamos estudando esse sério motivo de estudarmos sobre os atributos de Deus, é…</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
+      <c r="K115" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-sabedoria-de-deus-leivison-rosa-serie-atributos-divinos</t>
         </is>
       </c>
-      <c r="L115" s="2" t="inlineStr">
+      <c r="L115" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Eu9v9GN1OSs</t>
         </is>
@@ -7342,12 +7436,12 @@
         </is>
       </c>
       <c r="J116" s="4" t="inlineStr"/>
-      <c r="K116" s="2" t="inlineStr">
+      <c r="K116" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-onisciencia-de-deus-fabiano-krehnke-serie-atributos-divinos</t>
         </is>
       </c>
-      <c r="L116" s="2" t="inlineStr">
+      <c r="L116" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=6zMeUIeby3Q</t>
         </is>
@@ -7397,12 +7491,12 @@
           <t>…ilhos naturais ou espirituais. Vamos ler esses dois textos. Genesis 1, 28. Se você tem sua bíblia, abram Genesis 1, 28, que é uma das palavras que Deus dá para o homem e para a mulher e diz assim. Me escute. Antes de eu falar iss…</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr">
+      <c r="K117" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-imutabilidade-de-deus-lucas-balzer-serie-atributos-divinos</t>
         </is>
       </c>
-      <c r="L117" s="2" t="inlineStr">
+      <c r="L117" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=XnAK2YA9HUU</t>
         </is>
@@ -7457,12 +7551,12 @@
           <t>…e trouxe a sua Bíblia ou está com ela no seu solar, abre em romanos, pode projetar para a gente, romanos capítulo 11, verso 33, e a palavra do Senhor diz o seguinte, ó profundidade das riquezas, da sabedoria e do conhecimento d…</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
+      <c r="K118" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-infinitude-de-deus-willian-amaral-serie-atributos-divinos</t>
         </is>
       </c>
-      <c r="L118" s="2" t="inlineStr">
+      <c r="L118" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=2nDOHfXO7ps</t>
         </is>
@@ -7512,12 +7606,12 @@
           <t>…você fala assim, aí, eu preciso orar, falei para o próximo capítulo. Então, ver esse é o tipo de livro, aí, eu não consigo orar. Leia esse livro que ele vai te ajudar bastante. Amém? Agora, Deus. Então, vamos lá aí para o nosso…</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr">
+      <c r="K119" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-eternidade-de-deus-leivison-rosa-serie-atributos-divinos</t>
         </is>
       </c>
-      <c r="L119" s="2" t="inlineStr">
+      <c r="L119" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=o9XTDlYx718</t>
         </is>
@@ -7559,12 +7653,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Rm 1.20ss</t>
+          <t>Rm 1.20ss? / Jó 41.11</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Incerto — revisar (fontes divergem)</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -7572,14 +7666,19 @@
           <t>…a do homem. Então também não é para provar que Deus existe. Romanos capítulo 1... Não precisa projetar, mas quiser abrir do verso 20 indiante. Eu lembro que quando estudamos Romanos, acho que ficamos três, quatro semanas em cim…</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
+      <c r="K120" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-autossuficiencia-de-deus-felipe-bartoszewski-serie-atributos-divinos</t>
         </is>
       </c>
-      <c r="L120" s="2" t="inlineStr">
+      <c r="L120" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ZKDIEEEb1U8</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Jó 41:11; Hebreus 2:1</t>
         </is>
       </c>
     </row>
@@ -7632,12 +7731,12 @@
           <t>…não se citar com a Bíblia à sua versão impresso ou digital, João Capítulo 1, do verse 1 ou 3, nós vamos começar por um atributo hoje que se chama a auto existência de Deus, ok? Então porque Deus existe ou de que o Fórmula ex…</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr">
+      <c r="K121" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-autoexistencia-de-deus-willian-amaral-serie-atributos-divinos</t>
         </is>
       </c>
-      <c r="L121" s="2" t="inlineStr">
+      <c r="L121" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=LjRm7Il2IMc</t>
         </is>
@@ -7687,12 +7786,12 @@
           <t>…istória de Israel é extremamente singular. Então, nós falaríamos em 6 mil anos, basicamente, a história. Mas o cristianismo tem 2 mil anos. O que nós precisamos entender é que não há necessidade de procurar nos trazer alguma cois…</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
+      <c r="K122" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/solus-christus-leandro-vieira-serie-reformados</t>
         </is>
       </c>
-      <c r="L122" s="2" t="inlineStr">
+      <c r="L122" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ck8D5CTFyvc</t>
         </is>
@@ -7734,7 +7833,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Is 6.3</t>
+          <t>Ef 2.1-10</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7747,14 +7846,19 @@
           <t>…ia dele, é o que redunda em honra a Ele. Então, perceba que Isaia 6, 3, por exemplo, nós temos esse texto aí, nós vamos ver essas duas coisas nesse texto. Você pode abra a sua bíblia e junto comigo para a gente acompanhar?…</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr">
+      <c r="K123" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/soli-deo-gloria-fabiano-krehnke-serie-reformados</t>
         </is>
       </c>
-      <c r="L123" s="2" t="inlineStr">
+      <c r="L123" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=UF5wwNcBeCo</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Efésios 2:1-10; 1 Coríntios 10:31; Colossenses 1:15-17</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7911,12 @@
           <t>…Então eu gostaria de ler um texto com vocês, a gente fez os capítulo 1, versículo 3 em diante. Vamos do 3 em diante. Bendito Deus e pai de nosso Senhor Jesus Cristo, qual nos abençoou com todas as bençãospirituais nos lugares ce…</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr">
+      <c r="K124" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sola-gratia-leandro-vieira-serie-reformados</t>
         </is>
       </c>
-      <c r="L124" s="2" t="inlineStr">
+      <c r="L124" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Dn8qzLYPReQ</t>
         </is>
@@ -7867,12 +7971,12 @@
           <t>…ersar na sola, que é chamada de sola fide ou somente a fé. Vamos para isso ao romano, capítulo 4, versículo 3 a 5. Será esse o nosso texto, base? As escrituras dizem assim, pois que diz a escritura? Abraham creu em Deus, e isso lhe foi imputado para just…</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr">
+      <c r="K125" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sola-fide-leandro-vieira-serie-reformados</t>
         </is>
       </c>
-      <c r="L125" s="2" t="inlineStr">
+      <c r="L125" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=w2SvKVdORKs</t>
         </is>
@@ -7927,12 +8031,12 @@
           <t>…você ouvir agora o Silo da Família dos Creteles. Segundo a Atimote, capítulo 3, versículo 16 e 17, as escrituras dizem assim. Toda a escritura é inspirada por Deus e útil para o ensino, para a repreensão, para a correção, pa…</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr">
+      <c r="K126" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sola-scriptura-leandro-vieira-serie-reformados</t>
         </is>
       </c>
-      <c r="L126" s="2" t="inlineStr">
+      <c r="L126" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=vN7v9tT5g7Q</t>
         </is>
@@ -7978,12 +8082,12 @@
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr"/>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="K127" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-cosmovisao-crista-fabiano-krehnke-serie-reformados</t>
         </is>
       </c>
-      <c r="L127" s="2" t="inlineStr">
+      <c r="L127" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=pC61UslmG6o</t>
         </is>
@@ -8034,12 +8138,12 @@
         </is>
       </c>
       <c r="J128" s="4" t="inlineStr"/>
-      <c r="K128" s="2" t="inlineStr">
+      <c r="K128" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-metanarrativa-fabiano-krehnke-serie-reformados</t>
         </is>
       </c>
-      <c r="L128" s="2" t="inlineStr">
+      <c r="L128" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=NzE3hA3UWxE</t>
         </is>
@@ -8094,12 +8198,12 @@
           <t>…abri as escrituras na Carta que Paulo escreve aos efeios no capítulo 1, no versículo 15. Quando nós olhamos para essa escritura, nós percebemos a importância da reso reição. Paulo após saudar os efeios e falar a respeito daquilo…</t>
         </is>
       </c>
-      <c r="K129" s="2" t="inlineStr">
+      <c r="K129" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/ressureicao-vida-apos-a-vida-apos-a-morte-leandro-vieira-serie-pascoa-em-familia</t>
         </is>
       </c>
-      <c r="L129" s="2" t="inlineStr">
+      <c r="L129" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ogy0ftArloM</t>
         </is>
@@ -8154,12 +8258,12 @@
           <t>…. Por isso eu gostaria de convidar a abrir a sua Bíblia, em Mateus, capítulo 16 do verso 21 até o verso 25. Esse texto é um texto muito conhecido por todos nós, é o texto, aonde Jesus, ele diz que era necessário ir a Jerusalém…</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr">
+      <c r="K130" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/exaltando-o-significado-da-cruz-de-cristo-felipe-bartosweski-serie-pascoa-em-familia</t>
         </is>
       </c>
-      <c r="L130" s="2" t="inlineStr">
+      <c r="L130" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=d1iPjpXYmZE</t>
         </is>
@@ -8214,12 +8318,12 @@
           <t>…re nós. Abra a sua bíblia, se você puder comigo em casa, em Mateus, o capítulo 11, Mateus 11, os versículos 28 até 30, eu vou pedir para já que ler aqui daqui a pouco. Esse texto, Ele vai falar justamente sobre o que Jesus vei…</t>
         </is>
       </c>
-      <c r="K131" s="2" t="inlineStr">
+      <c r="K131" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/quaresma-ser-humano-com-nosso-deus-humano-fabiano-krehnke-serie-pascoa-em-familia</t>
         </is>
       </c>
-      <c r="L131" s="2" t="inlineStr">
+      <c r="L131" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=OY-oB33RCPk</t>
         </is>
@@ -8274,12 +8378,12 @@
           <t>…começar, nós queremos ler juntos um texto o qual usamos de exo do capítulo 12. Eu vou pedir para o Leandro Vieira que lê com a gente. Os primeiros de quatro versículos só que a gente vai ter um contexto um pouco da pássica…</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
+      <c r="K132" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/quaresma-a-jornada-para-a-pascoa-fabiano-krehnke-serie-pascoa-em-familia</t>
         </is>
       </c>
-      <c r="L132" s="2" t="inlineStr">
+      <c r="L132" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=p1MUwBaKYDI</t>
         </is>
@@ -8334,12 +8438,12 @@
           <t>…vindo você ouvir agora o Círuga Família dos Cretes. Dindo o capítulo 2, versículo 11, as escrituras dizem assim, porque a graça de Deus se manifestou salvadora a todos os homens, educándonos para que, renegadas a impiedade e as…</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
+      <c r="K133" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/vida-crista-coerente-leandro-vieira-minisserie-parte-04</t>
         </is>
       </c>
-      <c r="L133" s="2" t="inlineStr">
+      <c r="L133" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=OlIZQBg1-Ug</t>
         </is>
@@ -8394,12 +8498,12 @@
           <t>…bem-vindo você ouvir agora o Silo da Família dos que preio. Tito 2, versículo 11, porque a graça salvadora de Deus se ha manifestado a todos os homens, ensinando nos quê, renunciando a impiedade e as concurciências mundanas,…</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
+      <c r="K134" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/vida-crista-coerente-leandro-vieira-minisserie-parte-03</t>
         </is>
       </c>
-      <c r="L134" s="2" t="inlineStr">
+      <c r="L134" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=mkoKCQstVvw</t>
         </is>
@@ -8454,12 +8558,12 @@
           <t>…você ouvirá agora o sinor da família dos que prena. Tinto, capítulo 2 é o nosso texto base, versículo 11 em diante. As escrituras dizem assim, porque a graça salvadora de Deus se amanefestado a todos os homens, ensinando nos qu…</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr">
+      <c r="K135" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/vida-crista-coerente-leandro-vieira-minisserie-parte-02</t>
         </is>
       </c>
-      <c r="L135" s="2" t="inlineStr">
+      <c r="L135" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=NYzeGf1jfDA</t>
         </is>
@@ -8514,12 +8618,12 @@
           <t>…ndo você ouvir agora o Círro da Família dos Quepreia. Tipo, Capítulo 2, versículo 11, porque a graça de Deus se ha manifestado a todos os homens, ou a graça salvadora de Deus, se ha manifestado a todos os homens. Ensinando nos q…</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
+      <c r="K136" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/vidacristacoerenteparte01</t>
         </is>
       </c>
-      <c r="L136" s="2" t="inlineStr">
+      <c r="L136" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=cCIJphobz14</t>
         </is>
@@ -8561,7 +8665,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Rm 8.5</t>
+          <t>Ap 3.14-22</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8574,14 +8678,19 @@
           <t>…a fome por Deus, essa fome ela é gerada por Deus, romano os capítulos oito versus cinco, diz assim, aquele que vive segundo a carne tem a mente voltada para o que a carne deseja, mas quem, de acordo com o espírito, tem a mente v…</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr">
+      <c r="K137" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200529-barto-serie-7-audio</t>
         </is>
       </c>
-      <c r="L137" s="2" t="inlineStr">
+      <c r="L137" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=18nNFSZxOtk</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Apocalipse 3:14-22; Cânticos 5; Mateus 16:21</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8730,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Jd 4</t>
+          <t>Pv 1.7; Is 66.2</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8634,14 +8743,19 @@
           <t>…mos adiante. Existe uma característica citada pelo apóstolo Judas, capital 1,4 diz o seguinte, por quanto certos indivíduos cuja condenação já estava sentenciada muito tempo, infiltraram-se em nossa congregação com toda espéc…</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="K138" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200525-william-6-palavra-serie-audio</t>
         </is>
       </c>
-      <c r="L138" s="2" t="inlineStr">
+      <c r="L138" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=hB4zV5R3ins</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Provérbios 1:7; Isaías 66:2; Lucas 18:9-14; Mateus 28:8</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8808,12 @@
           <t>…começar eu gostaria que você abrícia a sua bibliocumibu em Romanos 11, o 1º versículo do 1º versículo do 1º versículo da carta aos ebreus. Ora, a fé é a certeza de coisas que se esperam, a convicção de fatos que se não venha. En…</t>
         </is>
       </c>
-      <c r="K139" s="2" t="inlineStr">
+      <c r="K139" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200512-fafa-5-palavra-audio</t>
         </is>
       </c>
-      <c r="L139" s="2" t="inlineStr">
+      <c r="L139" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=EDPLR0tClS4</t>
         </is>
@@ -8745,12 +8859,12 @@
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr"/>
-      <c r="K140" s="2" t="inlineStr">
+      <c r="K140" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200505-leivison-rosa-4-palavra-audio</t>
         </is>
       </c>
-      <c r="L140" s="2" t="inlineStr">
+      <c r="L140" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=oAzzLoP-S5Y</t>
         </is>
@@ -8800,12 +8914,12 @@
           <t>…de Deus, embora as escrituras, por exemplo, como o livro de apocalipse capítulo 1, vai falar da aparência física de Jesus Cristo, né, e alguns outros salmos também vão falar textos relacionados a isso, nós não podemos resumir a beleza de D…</t>
         </is>
       </c>
-      <c r="K141" s="2" t="inlineStr">
+      <c r="K141" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200428-barto-3-palavra-serie-audio</t>
         </is>
       </c>
-      <c r="L141" s="2" t="inlineStr">
+      <c r="L141" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jlzbE6Q-uiA</t>
         </is>
@@ -8847,12 +8961,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Hb 6.4ss; 1Co 3.16</t>
+          <t>1Jo 4.9-11; 2Co 5.17; Gl 2.20 (vários textos)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Temático / vários textos</t>
         </is>
       </c>
       <c r="J142" s="4" t="inlineStr">
@@ -8860,14 +8974,19 @@
           <t>…lguém morando e habitando em alguém. Paulo, aos corintos no capítulo 13 da primeira carta aos corintos, ele vai falar sobre os mais variados Domes e as mais variadas manifestações desses Domes, mas ele vai falar que nenhum deles…</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
+      <c r="K142" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200423-fafa-2-palavra-serie-audio</t>
         </is>
       </c>
-      <c r="L142" s="2" t="inlineStr">
+      <c r="L142" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=8pgNBz1aqGM</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>1 João 4:9-11; 2 Coríntios 5:17; Gálatas 2:20</t>
         </is>
       </c>
     </row>
@@ -8915,12 +9034,12 @@
           <t>…r, eu dei uma olhada em algumas pesquisas dos anos 80, nós vamos perceber que nos anos 80 os pastores ministros religiosos, nos 80 e 90, eram uma das profissões mais confiáveis. Então o povo tinha muita confiança em um pastor, em alguém que era alg…</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr">
+      <c r="K143" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/afeicoes</t>
         </is>
       </c>
-      <c r="L143" s="2" t="inlineStr">
+      <c r="L143" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=h6kG6XdFdhw</t>
         </is>
@@ -8962,12 +9081,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Tt 2.11ss</t>
+          <t>Tt 2.11-14; Ef 2.1-3; Rm 3.9-24</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J144" s="4" t="inlineStr">
@@ -8975,14 +9094,19 @@
           <t>…em-vindo você ouvir agora o Silo da Família dos que treino. Tito Capítulo 2, versões, porque a graça de Deus se ha manifestado, trazendo salvação a todos os homens, 12, ensinando nos quê, renunciando a impiedade e as circunc…</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr">
+      <c r="K144" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/leandro-edicao-audio</t>
         </is>
       </c>
-      <c r="L144" s="2" t="inlineStr">
+      <c r="L144" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=2I3UYBVORIU</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Tito 2:11-14; Efésios 2:1-3; Romanos 3:9-24</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9159,12 @@
           <t>…mas eu quero ser aqui bem pragmático, só um cento e quinze versículo três. Só um cento e quinze, cento e quinze versículo três. Hoje chegamos então do descende, eu estava revisando a palavra e eu estava fazendo isso ao som de gr…</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr">
+      <c r="K145" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/leandro-edicao-audio-1</t>
         </is>
       </c>
-      <c r="L145" s="2" t="inlineStr">
+      <c r="L145" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=bEPcQntD4gw</t>
         </is>
@@ -9090,12 +9214,12 @@
           <t>…antigo testamento, você vai ver, especialmente, no livro de Levítico, você vai perceber nos capítulos, vários capítulos, eu não me engano os primeiros, eu não tenho certeza agora, mas você vai ver muito sobre a espiação e os sacrifícios que eram feitos. Então…</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
+      <c r="K146" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200216-fafa-audio</t>
         </is>
       </c>
-      <c r="L146" s="2" t="inlineStr">
+      <c r="L146" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=CBUGsbBgklc</t>
         </is>
@@ -9150,12 +9274,12 @@
           <t>…or aqui para na projeção, mas é só para você ouvir a notar. Mateus, capítulo 24, verso 22. Mas por causa dos eleitos, tais dias serão abreviados. Marcos, capítulo 8, verso 22. Para enganar se possível os próprios eleitos. Mate…</t>
         </is>
       </c>
-      <c r="K147" s="2" t="inlineStr">
+      <c r="K147" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200223-palavra-completa-barto-audio</t>
         </is>
       </c>
-      <c r="L147" s="2" t="inlineStr">
+      <c r="L147" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=lLoeqcxgzWY</t>
         </is>
@@ -9210,12 +9334,12 @@
           <t>…vindo, você ouvirá agora o Silvia Família dos que creio. Os Romanos, capítulo 8, versículo 30, quem encontrou, diga assim, e aos que predestinou, a esses também chamou, e aos que chamou, a esses também justificou, e aos que jus…</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr">
+      <c r="K148" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/perseveranca-dos-santos-leandro-vieira-serie-as-doutrinas-da-graca</t>
         </is>
       </c>
-      <c r="L148" s="2" t="inlineStr">
+      <c r="L148" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=R1aoidSFbwM</t>
         </is>
@@ -9261,12 +9385,12 @@
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr"/>
-      <c r="K149" s="2" t="inlineStr">
+      <c r="K149" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200308-fabiano-krehnke-audio</t>
         </is>
       </c>
-      <c r="L149" s="2" t="inlineStr">
+      <c r="L149" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=qsoTzJgw_sI</t>
         </is>
@@ -9308,7 +9432,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Sl 90.12</t>
+          <t>Sl 46.10</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9321,14 +9445,19 @@
           <t>…um plano de um começo de ano, mas se trata de uma vida. Em salmos 92, diz assim, ensina nos contar os nossos dias como o Fafa falou na semana passada. Aqui está falando sobre dias e não sobre anos. Por isso, não adianta nós…</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr">
+      <c r="K150" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/jaque-audio</t>
         </is>
       </c>
-      <c r="L150" s="2" t="inlineStr">
+      <c r="L150" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=6SvHkNLf_J8</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Salmo 46:10</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9506,12 @@
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr"/>
-      <c r="K151" s="2" t="inlineStr">
+      <c r="K151" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/disciplina-da-comunidade-leandro-alves-mini-serie-solitude-comunidade</t>
         </is>
       </c>
-      <c r="L151" s="2" t="inlineStr">
+      <c r="L151" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=ES9iFm7IZQE</t>
         </is>
@@ -9437,12 +9566,12 @@
           <t>…e aos irmãos que estavam na Galácia. Então tome sua bíblia, gálatas capítulo 1. Espero terminar hoje essa palavra, senão. Terminamos a próxima semana, mas acredito que eu consigo terminar hoje. Galatas capítulo 1. Hoje nós vamo…</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr">
+      <c r="K152" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sindrome-dos-galatas-leandro-vieira</t>
         </is>
       </c>
-      <c r="L152" s="2" t="inlineStr">
+      <c r="L152" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Q-fSPBY7eLI</t>
         </is>
@@ -9484,7 +9613,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Gl 1</t>
+          <t>Gl 3.15-25</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9497,14 +9626,19 @@
           <t>…la para nossa edificação. Então, estamos expondo a Ipislaus Galatas, eu fui até o capítulo 3, hoje eu vou tornar um pouquinho em fatizar um pouco o capítulo 1, mas basicamente qual era o problema acontecendo na igreja da Galáci…</t>
         </is>
       </c>
-      <c r="K153" s="2" t="inlineStr">
+      <c r="K153" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sindrome-dos-galatas-parte-02-leandro-vieira</t>
         </is>
       </c>
-      <c r="L153" s="2" t="inlineStr">
+      <c r="L153" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7KUDrbdAhOw</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Gálatas 3:15-25; Mateus 5:17; Jeremias 31:31-34; 1 Coríntios 2:6-16</t>
         </is>
       </c>
     </row>
@@ -9557,12 +9691,12 @@
           <t>…m literatura. Amém? Por favor, irmão. Dedique tempo. Vamos agálatas. Capítulo 1. Galatas Capítulo 1, quem encontrou e diga assim. Então, qual é o tema da palavra, as síndromes dos galatas do Evangelho, para o legalismo e libert…</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
+      <c r="K154" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sindrome-dos-galatas-parte-03-leandro-vieira</t>
         </is>
       </c>
-      <c r="L154" s="2" t="inlineStr">
+      <c r="L154" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=qMRyQ6JDeZc</t>
         </is>
@@ -9617,12 +9751,12 @@
           <t>…ja bem-vindo, você ouvir agora o Silvia Família dos Cretes. Galatas capítulo 3, versículo 1 em diante, as escrituras dizem assim, é óins sensatos, galatas, quem vos emfeite sol para não obedecer a verdade a voz, peram de os olh…</t>
         </is>
       </c>
-      <c r="K155" s="2" t="inlineStr">
+      <c r="K155" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sindrome-dos-galatas-parte-04-leandro-vieira</t>
         </is>
       </c>
-      <c r="L155" s="2" t="inlineStr">
+      <c r="L155" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=3GW5u0hcg5g</t>
         </is>
@@ -9677,12 +9811,12 @@
           <t>…a que se abre esqueci disso então gente abre a escritura em Mateus capítulo 16 vamos ver do verso 13 vamos fazer uma leitura dinâmica e aí depois retornaremos aos pontos que eu desejo ressaltar o vanjel de Mateus capítulo 16 o…</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr">
+      <c r="K156" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/introducao-aos-fundamentos-do-novo-testamento-leandro-vieira</t>
         </is>
       </c>
-      <c r="L156" s="2" t="inlineStr">
+      <c r="L156" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=X7jGPttaO5g</t>
         </is>
@@ -9737,12 +9871,12 @@
           <t>…como Pedro fala? Você, tu é o Cristo, o filho do Deus vivo, versículo 16, tu é o Cristo, o filho do Deus vivo, automaticamente assim que Pedro fala isso, Jesus vem e fala quem Ele é, percebe? Então Pedro recl...…</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr">
+      <c r="K157" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/fundamentos-do-novo-testamento-fabiano-krehnke</t>
         </is>
       </c>
-      <c r="L157" s="2" t="inlineStr">
+      <c r="L157" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=0Qj2iO2fWR8</t>
         </is>
@@ -9797,12 +9931,12 @@
           <t>…Pra que a gente possa começar da forma correta, vamos abrir Mateus Capítulo 16 e eu vou diretamente aos textos que falam a respeito desses quatro fundamentos e vamos compartilhar. Primeiro versículo, o 16, 16, 16, 2 evangelho…</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr">
+      <c r="K158" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/fundamentos-cristo-parte-02-leandro-vieira</t>
         </is>
       </c>
-      <c r="L158" s="2" t="inlineStr">
+      <c r="L158" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=XNM_xEO_eaM</t>
         </is>
@@ -9844,12 +9978,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>1Co 3.10-11; Gn 12; 17</t>
+          <t>Mt 16.13-18</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -9857,14 +9991,19 @@
           <t>…. Eu gostaria somente que você anotasse o texto de primeiro Corinthians, capítulo 3, verso 10 e 11, que fala sobre Cristo, sendo a licer-se e efésios dois-vinte, que traz Cristo como fundamento dos apóstolos e dos profetas, o…</t>
         </is>
       </c>
-      <c r="K159" s="2" t="inlineStr">
+      <c r="K159" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/fundamentos-igreja-leandro-alves</t>
         </is>
       </c>
-      <c r="L159" s="2" t="inlineStr">
+      <c r="L159" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-vmjd4zLRH4</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Mateus 16:13-18; Hebreus 3:1-6; Atos 2:42</t>
         </is>
       </c>
     </row>
@@ -9917,12 +10056,12 @@
           <t>…reciso de tempo hoje. E eu quero que comecemos por primeira corinte os capítulos 1, versículo 23. Essa é das antiga. Essa é das antiga. Se não for, não dá, não. Eu queria tanto cantar, irmão. Consigo, irmão. Consigo, irmão. E…</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr">
+      <c r="K160" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/fundamentos-cruz-parte-01-leandro-vieira</t>
         </is>
       </c>
-      <c r="L160" s="2" t="inlineStr">
+      <c r="L160" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=00rx_NzGu70</t>
         </is>
@@ -9977,12 +10116,12 @@
           <t>…s que é a cruz, e uma coisa que eu quero de novo ressaltar, Galatas Capítulo 3, por favor, versículo 1. Corre um pouquinho mais hoje, irmão. Galatas Capítulo 3, verso 1, nós abordamos esse texto na semana passada, já é uma das…</t>
         </is>
       </c>
-      <c r="K161" s="2" t="inlineStr">
+      <c r="K161" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/fundamentos-cruz-parte-02-leandro-vieira</t>
         </is>
       </c>
-      <c r="L161" s="2" t="inlineStr">
+      <c r="L161" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=2G_aK81vYpo</t>
         </is>
@@ -10024,12 +10163,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Mc 1.15; Lc 11.20; 22.18</t>
+          <t>Mc 1.15; Lc 11.20</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J162" s="4" t="inlineStr">
@@ -10037,14 +10176,19 @@
           <t>…. Então, precha atenção. No início do Ministério do Cristo, marcos capitulo 1, verso 15, o Senhor disse, o tempo foi comprido e o reino de Deus está próximo a rependeivos e crede no Evangelho. Qual é a primeira evidência do re…</t>
         </is>
       </c>
-      <c r="K162" s="2" t="inlineStr">
+      <c r="K162" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/fundamentos-reino-leandro-vieira</t>
         </is>
       </c>
-      <c r="L162" s="2" t="inlineStr">
+      <c r="L162" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=TaBRibliwSE</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Marcos 1:15; Lucas 11:20; Marcos 10:29-30</t>
         </is>
       </c>
     </row>
@@ -10084,12 +10228,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Mt 16 (contexto)</t>
+          <t>Mt 16.13-28</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
@@ -10097,14 +10241,19 @@
           <t>…ntos, gente. Então, vamos falar sobre o contexto geral, né? Mateus, capítulo 16, Jesus está falando sobre a edificação da igreja. Ele está lançando os quatro fundamentos pelo qual o novo testamento ele está alicersado. Então,…</t>
         </is>
       </c>
-      <c r="K163" s="2" t="inlineStr">
+      <c r="K163" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/fundamentos-reino-parte-2-felipe-bartoszewski</t>
         </is>
       </c>
-      <c r="L163" s="2" t="inlineStr">
+      <c r="L163" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=sYDC9JZC7xU</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Mateus 16:13-28; Romanos 14:17; Gênesis 3</t>
         </is>
       </c>
     </row>
@@ -10144,12 +10293,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Mc 1.15; Lc 11.20; 22.18</t>
+          <t>Mt 5.17-20?</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Incerto — revisar (fontes divergem)</t>
         </is>
       </c>
       <c r="J164" s="4" t="inlineStr">
@@ -10157,14 +10306,19 @@
           <t>…esta ideia, com esse entendimento, e aí entramos o texto de Marcos, capítulo 1, onde o Leandro falou sobre a chegada do reino. Então se você quiser notar, estiver notando só para gente trazer uma introdução para aqueles que nã…</t>
         </is>
       </c>
-      <c r="K164" s="2" t="inlineStr">
+      <c r="K164" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/fundamentos-reino-parte-3-leandro-alves</t>
         </is>
       </c>
-      <c r="L164" s="2" t="inlineStr">
+      <c r="L164" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=6O7tAVbxCqA</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Mateus 5:1-48; Mateus 5:17-20; Hebreus 10:16 (o áudio do podcast cita Mc 1.15; Lc 11.20; 22.18)</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10357,7 @@
         </is>
       </c>
       <c r="J165" s="4" t="n"/>
-      <c r="L165" s="2" t="inlineStr">
+      <c r="L165" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jFc2sOuPvys</t>
         </is>
@@ -10245,7 +10399,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Ap 21.1-4</t>
+          <t>Ef 1.10; Cl 1.20; Rm 8.18-23; Êx 19.5-6</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10258,14 +10412,19 @@
           <t>…r e se alinhar com de baixo. É isso que as escrituras dizem apocalipse 21-1 a 4. Só que cremos por tanto tempo na fábula que a verdade sou a como uma fábula, porque gente, porque a gente acha um absurdo a palavra, porque nós passa…</t>
         </is>
       </c>
-      <c r="K166" s="2" t="inlineStr">
+      <c r="K166" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/introducao-ao-sacerdocio</t>
         </is>
       </c>
-      <c r="L166" s="2" t="inlineStr">
+      <c r="L166" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=wfEECmMTLGY</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Efésios 1:10; Colossenses 1:20; Romanos 8:18-23; Êxodo 19:5-6</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10469,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
@@ -10318,14 +10477,19 @@
           <t>…o mediador, porque quando Deus desceu no monte, eu quero o exo do capítulo 19, é a primeira vez que nós vamos encontrar essa proposta de Deus ao povo hebreu. Vou pregar mais para não contar muita história ruim de mim, né?…</t>
         </is>
       </c>
-      <c r="K167" s="2" t="inlineStr">
+      <c r="K167" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/introducao-ao-sacerdocioparte-2-leandro-vieira-serie-ceus-igreja-terra</t>
         </is>
       </c>
-      <c r="L167" s="2" t="inlineStr">
+      <c r="L167" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=sBcT0rBSvIw</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Êxodo 19:5-6; Jeremias 7:21-28; 1 Pedro 2:9-10; Apocalipse 5:8-10; Ezequiel 28:11-19</t>
         </is>
       </c>
     </row>
@@ -10365,12 +10529,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>At 13?</t>
+          <t>At 13.1-3</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Incerto — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J168" s="4" t="inlineStr">
@@ -10378,14 +10542,19 @@
           <t>…eal, tocando a vida um do outro, na família de fé. E acreditamos que agora, em 2019, a partir desse ano, e dessa nova estação, nós vamos começar a viver um pouco mais do sacerdócio ao mundo, porque algumas coisas já foram restauradas em nós…</t>
         </is>
       </c>
-      <c r="K168" s="2" t="inlineStr">
+      <c r="K168" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/sacerdocio-ao-senhor-fabiano-krehnke-serie-ceus-igreja-terra</t>
         </is>
       </c>
-      <c r="L168" s="2" t="inlineStr">
+      <c r="L168" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=bUTWyI6KFH8</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Efésios 1-3; Atos 13:1-3; Gênesis 1:26-28; Romanos 8:20-21; Mateus 6:9-13; Hebreus 5:7</t>
         </is>
       </c>
     </row>
@@ -10425,7 +10594,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Gn 3.7</t>
+          <t>Ap 5.8-10</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10438,14 +10607,19 @@
           <t>…de, mas a motivação relacional se perdeu. Olha o que dizem, Genesis 3 vs 7. Abriu-se então os olhos de ambos, percebendo que estavam nos fos de figueiras e fizerem cintas para ser. Só que todo mundo sabe que isso aconteceu quan…</t>
         </is>
       </c>
-      <c r="K169" s="2" t="inlineStr">
+      <c r="K169" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/barto</t>
         </is>
       </c>
-      <c r="L169" s="2" t="inlineStr">
+      <c r="L169" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=4EC7K5cfSt4</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Apocalipse 5:8-10; Mateus 16:21-26; Colossenses 1:24; Efésios 3:18-19; Filipenses 2:1-12</t>
         </is>
       </c>
     </row>
@@ -10485,12 +10659,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Nm 18.7; 20?</t>
+          <t>Nm 20.7-13</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Incerto — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J170" s="4" t="inlineStr">
@@ -10498,14 +10672,19 @@
           <t>…tendeu? É um projeto por... Quarta para 18 lá, Rosinha. Põe números 18 para... Números 20, 23. Versículo 7, desculpa, Rosa. É que o texto vai até o 23. Falou o Senhor a Moisésia dizendo. Toma a tua vara, ajuda a congregação, tu…</t>
         </is>
       </c>
-      <c r="K170" s="2" t="inlineStr">
+      <c r="K170" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-sacerdocio-ao-mundo-leandro-vieira-serie-ceus-igreja-terra</t>
         </is>
       </c>
-      <c r="L170" s="2" t="inlineStr">
+      <c r="L170" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=lM3C5cCx-GI</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Efésios 1:10; Colossenses 1:20; Números 20:7-13; Ezequiel 8:3; Números 16:41-50</t>
         </is>
       </c>
     </row>
@@ -10545,12 +10724,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>At 20.24; Lc 4.14ss</t>
+          <t>At 20.24; Lc 4.43; Ap 14.6</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
@@ -10558,14 +10737,19 @@
           <t>…r nisso. Eu gostaria que você abri-se a sua bíblia em Artes Capítulo 20. Se a Joa esconseguir me ajudar a ver ciclo 24. Nas próximas, eu vou melhorar a Joa e se eu vou te dar alguns textos, porque é muito difícil essa coisa de f…</t>
         </is>
       </c>
-      <c r="K171" s="2" t="inlineStr">
+      <c r="K171" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/introducao-ao-evangelho</t>
         </is>
       </c>
-      <c r="L171" s="2" t="inlineStr">
+      <c r="L171" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=QxtHkz5SAIo</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Atos 20:24; Lucas 4:43; Apocalipse 14:6; 1 Tessalonicenses 1:10</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10789,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>At 5.20</t>
+          <t>At 20.24; Ef 1.3-6; Tt 2.11-12</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10618,14 +10802,19 @@
           <t>…ue o evo engenho promete Olha o que inscrito é desenhar Nos capítulo 5, versículo 20 A nos capítulo 5, versão 20 A cotação é dos discípulos Então manjo O versículo 109, 151, 181, 181 Abrei as cortas da prisão e tirá-los para for…</t>
         </is>
       </c>
-      <c r="K172" s="2" t="inlineStr">
+      <c r="K172" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-da-graca-02</t>
         </is>
       </c>
-      <c r="L172" s="2" t="inlineStr">
+      <c r="L172" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jK0nyp6LQQU</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Atos 20:24; Efésios 1:3-6; Tito 2:11-12</t>
         </is>
       </c>
     </row>
@@ -10678,12 +10867,12 @@
           <t>…tilhando, eu gostaria que pudéssemos começar com o texto de Marcos 1, versículo 15, Marcos 1, verso 15. De novo, eu não passei os teus pra jois, mas também eu acabei de me engajar. Perdi meu Aiped no Aiped, não avião, irmão, v…</t>
         </is>
       </c>
-      <c r="K173" s="2" t="inlineStr">
+      <c r="K173" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-da-graca-02</t>
         </is>
       </c>
-      <c r="L173" s="2" t="inlineStr">
+      <c r="L173" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7kcSQfFLTVo</t>
         </is>
@@ -10729,12 +10918,12 @@
         </is>
       </c>
       <c r="J174" s="4" t="inlineStr"/>
-      <c r="K174" s="2" t="inlineStr">
+      <c r="K174" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-do-reino-introducao-felipe-bartoszewski-serie-o-evangelho-completo</t>
         </is>
       </c>
-      <c r="L174" s="2" t="inlineStr">
+      <c r="L174" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=y_cunQKcwpU</t>
         </is>
@@ -10789,12 +10978,12 @@
           <t>…o Senhor. Então nós queremos tornar isso acessível a vocês. Salmo, capítulo 8, eu quero começar por aqui. Sem dúvida, é um dos textos mais bellos de toda a escritura, salmo 8. Versículo 3. Bom, vamos do verso 1. Salmo 8, vers…</t>
         </is>
       </c>
-      <c r="K175" s="2" t="inlineStr">
+      <c r="K175" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-do-reino-02</t>
         </is>
       </c>
-      <c r="L175" s="2" t="inlineStr">
+      <c r="L175" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=7hvXNgFZrW8</t>
         </is>
@@ -10836,12 +11025,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Hb 1.1-2; 2Tm 1.9</t>
+          <t>Ap 14.6; 2Tm 1.9</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J176" s="4" t="inlineStr">
@@ -10849,14 +11038,19 @@
           <t>…elou a Moisés na Sarsardente. Aí foi se revelar a Jusue, no capítulo 5, como um anjo com uma espada para fora da banhinha. Mas é interessante que nas duas vezes em que Deus se revelou em uma geração diferente, ele fala a mesma c…</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr">
+      <c r="K176" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-eterno-01</t>
         </is>
       </c>
-      <c r="L176" s="2" t="inlineStr">
+      <c r="L176" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=y9ZaScWDMEg</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Apocalipse 14:6; Atos 3:21; 2 Timóteo 1:9; Colossenses 3:1-5</t>
         </is>
       </c>
     </row>
@@ -10896,12 +11090,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>At 20.24</t>
+          <t>At 20.24; Lc 4.43; Ap 14.6</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
@@ -10909,14 +11103,19 @@
           <t>…que nós falamos até aqui. Então para tal, Rosa, por favor, atos 20, 24. Atos capítulo 20 e 24. Nós falamos que o Evangelho completo tem três capítulos. O Evangelho da graça, o Evangelho do reino e o Evangelho eterno. Então…</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr">
+      <c r="K177" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-completo-part08</t>
         </is>
       </c>
-      <c r="L177" s="2" t="inlineStr">
+      <c r="L177" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=sGmrOsnx6ac</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Atos 20:24; Lucas 4:43; Apocalipse 14:6; Atos 3:21; 2 Coríntios 5:17-20</t>
         </is>
       </c>
     </row>
@@ -10969,12 +11168,12 @@
           <t>…dade humana. O Evangelho é primeiro o Evangelho da Graça em Atos Capitulo 20, versículo 24. Nós lemos a respeito do Evangelho da Graça, ou seja, a boa notícia de que Deus salvou o mediante a Graça. O Evangelho também é o Eva…</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr">
+      <c r="K178" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-completo-part08</t>
         </is>
       </c>
-      <c r="L178" s="2" t="inlineStr">
+      <c r="L178" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=uXbjUd8J5DU</t>
         </is>
@@ -11015,7 +11214,7 @@
         </is>
       </c>
       <c r="J179" s="4" t="n"/>
-      <c r="L179" s="2" t="inlineStr">
+      <c r="L179" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=qXL1mkpAtu4</t>
         </is>
@@ -11056,7 +11255,7 @@
         </is>
       </c>
       <c r="J180" s="4" t="n"/>
-      <c r="L180" s="2" t="inlineStr">
+      <c r="L180" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=z_MSUPJTuNU</t>
         </is>
@@ -11097,7 +11296,7 @@
         </is>
       </c>
       <c r="J181" s="4" t="n"/>
-      <c r="L181" s="2" t="inlineStr">
+      <c r="L181" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=9Lc8RamwSfY</t>
         </is>
@@ -11138,7 +11337,7 @@
         </is>
       </c>
       <c r="J182" s="4" t="n"/>
-      <c r="L182" s="2" t="inlineStr">
+      <c r="L182" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=URLxnlIMpvc</t>
         </is>
@@ -11179,7 +11378,7 @@
         </is>
       </c>
       <c r="J183" s="4" t="n"/>
-      <c r="L183" s="2" t="inlineStr">
+      <c r="L183" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=y5RaaLVs4FY</t>
         </is>
@@ -11220,7 +11419,7 @@
         </is>
       </c>
       <c r="J184" s="4" t="n"/>
-      <c r="L184" s="2" t="inlineStr">
+      <c r="L184" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=37Ctc3FJ46k</t>
         </is>
@@ -11261,7 +11460,7 @@
         </is>
       </c>
       <c r="J185" s="4" t="n"/>
-      <c r="L185" s="2" t="inlineStr">
+      <c r="L185" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=T_Df7pxWru4</t>
         </is>
@@ -11297,7 +11496,7 @@
         </is>
       </c>
       <c r="J186" s="4" t="n"/>
-      <c r="L186" s="2" t="inlineStr">
+      <c r="L186" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=LVp1npjJ7Qk</t>
         </is>
@@ -11333,7 +11532,7 @@
         </is>
       </c>
       <c r="J187" s="4" t="n"/>
-      <c r="L187" s="2" t="inlineStr">
+      <c r="L187" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=G2Ggf1Mr4TI</t>
         </is>
@@ -11374,7 +11573,7 @@
         </is>
       </c>
       <c r="J188" s="4" t="n"/>
-      <c r="L188" s="2" t="inlineStr">
+      <c r="L188" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Te5QQIv4vuA</t>
         </is>
@@ -11410,7 +11609,7 @@
         </is>
       </c>
       <c r="J189" s="4" t="n"/>
-      <c r="L189" s="2" t="inlineStr">
+      <c r="L189" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=rnyN95QCvDg</t>
         </is>
@@ -11451,7 +11650,7 @@
         </is>
       </c>
       <c r="J190" s="4" t="n"/>
-      <c r="L190" s="2" t="inlineStr">
+      <c r="L190" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=rpUmvWkIKsw</t>
         </is>
@@ -11501,12 +11700,12 @@
           <t>…de convidar a todos os irmãos a abrir em as suas bíblias em Mateus no capítulo 28. Mateus no capítulo 28, a partir do versículo 18, leremos até o 20. Jesus aproximou-se deles e disse, toda a autoridade do céu e na terra me foi…</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr">
+      <c r="K191" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/santissima-trindade-o-coracao-da-fe-crista-lucas-gregory-domingo-da-trindade</t>
         </is>
       </c>
-      <c r="L191" s="2" t="inlineStr">
+      <c r="L191" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=NKKdKiz7wmI</t>
         </is>
@@ -11556,12 +11755,12 @@
           <t>…e Cristo e para o bem do mundo. Abra sua Bíblia no livro de Atos, no capítulo 2, vamos ler a aportão das escrituras hoje, um tanto mais resumida dos versos 1 a 4. Acompõe comigo na sua versão. Ao cumprício dia de Pentecostes…</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr">
+      <c r="K192" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-obra-do-espirito-santo-leandro-vieira-domingo-de-pentecostes</t>
         </is>
       </c>
-      <c r="L192" s="2" t="inlineStr">
+      <c r="L192" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=pF0FZpHwBUc</t>
         </is>
@@ -11616,12 +11815,12 @@
           <t>…romessa de que Deus habitaria nos homens e entre os homens. Atos capítulo 2, versículo 1. E comprindo-se o dia de Pentecostes, estavam todos concordemente no mesmo lugar. E de repente veio do céu um som, como de um vento veh…</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr">
+      <c r="K193" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-promessa-domingo-de-pentecostes-leandro-vieira</t>
         </is>
       </c>
-      <c r="L193" s="2" t="inlineStr">
+      <c r="L193" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=oWx6xxG1NwA</t>
         </is>
@@ -11676,12 +11875,12 @@
           <t>…sa semana. Nosso texto base para o nosso domingo de ramos é Marcos Capitluonze, versículo 1 ao 11 na primeira porção depois, 12 ao 17 mais para a conclusão do sermão. Se você tem a Bíblia, usia nós projetamos aqui para facilit…</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr">
+      <c r="K194" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/domingo-de-ramos-leandro-vieira</t>
         </is>
       </c>
-      <c r="L194" s="2" t="inlineStr">
+      <c r="L194" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=26zfthYH00I</t>
         </is>
@@ -11736,12 +11935,12 @@
           <t>…ra de Jesus. A memória, se vamos abrir a escritura em ex do capítulo 12, versículo 1, endiante, ex do capítulo 12, verso 1, endiante. Como nós já estamos na nossa série espojetiva de Galatas, Anátema ou outro Evangelho, estamos…</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr">
+      <c r="K195" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/pascoa-leandro-vieira-serie-anatema-o-outro-evangelho</t>
         </is>
       </c>
-      <c r="L195" s="2" t="inlineStr">
+      <c r="L195" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=zWz7sYLFNzU</t>
         </is>
@@ -11796,12 +11995,12 @@
           <t>…para os interesses de Cristo e para o bem do mundo. Segunda Reis, o capítulo 22, leremos do 8 até o 13. Assim, desapalávamos do Senhor em segundo a rei 22 e 8. Então, o sumo sacerdote e o queias disse ao secretário Safan. En…</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr">
+      <c r="K196" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/reforma-protestante-um-chamado-a-revitalizacao-fabiano-krehnke</t>
         </is>
       </c>
-      <c r="L196" s="2" t="inlineStr">
+      <c r="L196" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=1IQ5yMn0pis</t>
         </is>
@@ -11856,12 +12055,12 @@
           <t>…a do texto bíblico nessa manhã. A leitura será em primeiro atimótico, capítulo 4. Estamos nesse domingo importante, do mingo, em que geralmente na história do último domingo de outubro é celebrado. O domingo da reforma, nós…</t>
         </is>
       </c>
-      <c r="K197" s="2" t="inlineStr">
+      <c r="K197" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-palavra-fez-tudo-a-reforma-continua-fabiano-krehnke-reforma-protestante</t>
         </is>
       </c>
-      <c r="L197" s="2" t="inlineStr">
+      <c r="L197" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-w27SP_VFvQ</t>
         </is>
@@ -11897,7 +12096,7 @@
         </is>
       </c>
       <c r="J198" s="4" t="n"/>
-      <c r="L198" s="2" t="inlineStr">
+      <c r="L198" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-roaRFAQ0zM</t>
         </is>
@@ -11943,12 +12142,12 @@
         </is>
       </c>
       <c r="J199" s="4" t="inlineStr"/>
-      <c r="K199" s="2" t="inlineStr">
+      <c r="K199" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200112-willian-audio</t>
         </is>
       </c>
-      <c r="L199" s="2" t="inlineStr">
+      <c r="L199" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=MhZoZlmiPCs</t>
         </is>
@@ -11990,12 +12189,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Mt 4.23</t>
+          <t>Sl 115.1-8</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J200" s="4" t="inlineStr">
@@ -12003,14 +12202,19 @@
           <t>…é muito fácil de a gente ver isso na vida de Jesus, porque Mateus 4, verso 23, diz... A gente conhece o contexto. Mateus 4, Jesus 1, desde o início de Mateus, vai contando sobre a genealogia de Jesus Christ, Jesus esbatizado,…</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr">
+      <c r="K200" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20200105-lucas-balzer-audio-1</t>
         </is>
       </c>
-      <c r="L200" s="2" t="inlineStr">
+      <c r="L200" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=L5rJVhEWXKg</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Salmo 115:1-8; Ezequiel 33; João 3:1-8 (a descrição do vídeo também cita Sl 115)</t>
         </is>
       </c>
     </row>
@@ -12050,12 +12254,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Ap 1.1; Cl 1</t>
+          <t>Ap 1.1; Cl 1.15-20</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Provável — revisar</t>
+          <t>Confirmado (transcrição + NotebookLM)</t>
         </is>
       </c>
       <c r="J201" s="4" t="inlineStr">
@@ -12063,14 +12267,19 @@
           <t>…m-vindo, você ouvir agora o Ciro da Família dos Que Crelho. Apocalipse capítulo 1, a primeira parte do texto de Apocalipse, o último livro das escrituras diz, revelação de Jesus Cristo. Diga comigo, revelação de Jesus Cristo. Entã…</t>
         </is>
       </c>
-      <c r="K201" s="2" t="inlineStr">
+      <c r="K201" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20191222-leandro-vieira-audio</t>
         </is>
       </c>
-      <c r="L201" s="2" t="inlineStr">
+      <c r="L201" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=v1fndaLAbZw</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Apocalipse 1:1; Colossenses 1:15-20; João 14:9; Isaías 9:5-7; João 4:1-14</t>
         </is>
       </c>
     </row>
@@ -12123,12 +12332,12 @@
           <t>…deles, e faz uns 11 falando sobre isso. Então, vamos lá. Estamos lendo na NVI e fez uns 11. Nele, fomos também escolhidos. Tendo sido predestinados conforme o plano daquele que faz todas as coisas, segundo o propósito da... Vamos lá, dá? Sua vontade…</t>
         </is>
       </c>
-      <c r="K202" s="2" t="inlineStr">
+      <c r="K202" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/qual-e-a-vontade-de-deus-fabiano-krehnke</t>
         </is>
       </c>
-      <c r="L202" s="2" t="inlineStr">
+      <c r="L202" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Gu_kIv_YYi8</t>
         </is>
@@ -12183,12 +12392,12 @@
           <t>…o poder de Deus e o Espírito dessa época. Prata-o, vamos arromanos, capítulo 1, versículo 16. Vamos usar dois textos apenas, não será uma exposição, como temos feito. Porque não me envergonho do Evangelho de Cristo, pois é o p…</t>
         </is>
       </c>
-      <c r="K203" s="2" t="inlineStr">
+      <c r="K203" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20191201-leandro-vieira-audio</t>
         </is>
       </c>
-      <c r="L203" s="2" t="inlineStr">
+      <c r="L203" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=UGDcG6aW6d8</t>
         </is>
@@ -12243,12 +12452,12 @@
           <t>…ê ler um pouco a Bíblia, você vai lembrar de esse contexto. Atos 17, Paulo chega lá e ele vê várias imagens. Então, ele vê imagens de culto, imagens que eram cultuadas, que aquelas pessoas fazem orações e pedidos aqueles fal…</t>
         </is>
       </c>
-      <c r="K204" s="2" t="inlineStr">
+      <c r="K204" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/idolos-fafa</t>
         </is>
       </c>
-      <c r="L204" s="2" t="inlineStr">
+      <c r="L204" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=QAuP-DojDeg</t>
         </is>
@@ -12303,12 +12512,12 @@
           <t>…bem-vindo você ouvir agora o sinudo a família dos que prei atos capítulo 20 verso 20 indiante versículo 20, bom é quando Paulo está se despedindo dos presbíteros de F as um emileto esse é um texto muito singular e diz Paulo…</t>
         </is>
       </c>
-      <c r="K205" s="2" t="inlineStr">
+      <c r="K205" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20190825-leandro-vieira-audio</t>
         </is>
       </c>
-      <c r="L205" s="2" t="inlineStr">
+      <c r="L205" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=uWwBsE3mwE4</t>
         </is>
@@ -12349,7 +12558,7 @@
         </is>
       </c>
       <c r="J206" s="4" t="n"/>
-      <c r="L206" s="2" t="inlineStr">
+      <c r="L206" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=f-66VyYLImk</t>
         </is>
@@ -12390,7 +12599,7 @@
         </is>
       </c>
       <c r="J207" s="4" t="n"/>
-      <c r="L207" s="2" t="inlineStr">
+      <c r="L207" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=kpqtWTruD-0</t>
         </is>
@@ -12431,7 +12640,7 @@
         </is>
       </c>
       <c r="J208" s="4" t="n"/>
-      <c r="L208" s="2" t="inlineStr">
+      <c r="L208" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=yMJ11VbkhRU</t>
         </is>
@@ -12481,12 +12690,12 @@
           <t>…, eu escolhi um texto para a espor. E é a primeira pedra, o capítulo 5, versus 1 a 5. Não tem isso que eu acho que é a brange tanto, já o pressuposto de uma liderança plural e como isso deve acontecer na igreja. Primeira pedra,…</t>
         </is>
       </c>
-      <c r="K209" s="2" t="inlineStr">
+      <c r="K209" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/governo-plural-na-igreja-thiago-guerra-conferencia-repensando-igreja</t>
         </is>
       </c>
-      <c r="L209" s="2" t="inlineStr">
+      <c r="L209" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=I9wW6ZW6qUU</t>
         </is>
@@ -12536,12 +12745,12 @@
           <t>…o de serem proclamadoras, anunciadoras do Evangelho. Júnior capítulo 4, verso 28, até o verso 30, o texto bíblico na a história, evidentemente, da mulher Samaritana. Eu não vou entrar nos meandros culturais, mas vocês sabem, os…</t>
         </is>
       </c>
-      <c r="K210" s="2" t="inlineStr">
+      <c r="K210" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/como-ser-uma-igreja-missional-igor-miguel-conferencia-repensando-a-igreja</t>
         </is>
       </c>
-      <c r="L210" s="2" t="inlineStr">
+      <c r="L210" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=lqT8cZJMDuA</t>
         </is>
@@ -12591,12 +12800,12 @@
           <t>…texto bíblico antes da gente ir lá para a primeira timote. Genesis 1 de 26, 26 e 27 de seguinte. Deus diz, eu vou ler na versão NAA, diz a seguinte. Façamos o ser humano, eu gosto de NAA, que traz a palavra ser humano, em algu…</t>
         </is>
       </c>
-      <c r="K211" s="2" t="inlineStr">
+      <c r="K211" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/complementarismo-e-papeis-de-genero-cristiano-gaspar-conferencia-repensando-a-igreja</t>
         </is>
       </c>
-      <c r="L211" s="2" t="inlineStr">
+      <c r="L211" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=IRte3B9sV_k</t>
         </is>
@@ -12646,12 +12855,12 @@
           <t>…r responder essas perguntas olhando pro texto de efeitos de capítulo 2. Pesso que você abra sua bíblia em efeitos de capítulo 2, nós vamos andar por elas, pelo texto de efeitos dos dois, tentando responder algumas perguntas. A p…</t>
         </is>
       </c>
-      <c r="K212" s="2" t="inlineStr">
+      <c r="K212" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/soberania-de-deus-na-salvacao-filipe-niel-conferencia-repensando-a-igreja</t>
         </is>
       </c>
-      <c r="L212" s="2" t="inlineStr">
+      <c r="L212" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=EMNY0O9Yql0</t>
         </is>
@@ -12701,12 +12910,12 @@
           <t>…a a gente ler um texto muito clássico, cerca disso, Romano, capítulo 1. Nós vamos ler os versos de um a quatro e depois os versos de 16 e 17. Romano, capítulo 1, versos de um a quatro e 16 e 17. E vou pedir para que você mantém…</t>
         </is>
       </c>
-      <c r="K213" s="2" t="inlineStr">
+      <c r="K213" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/centralidade-do-evangelho-na-igreja-thiago-guerra-conferencia-repensando-a-igreja</t>
         </is>
       </c>
-      <c r="L213" s="2" t="inlineStr">
+      <c r="L213" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=4rTDZ-v7zO0</t>
         </is>
@@ -12756,12 +12965,12 @@
           <t>…ria abrir a Bíblia, te convidava você abrir a sua Bíblia em Apocalipse, Capitul 2, Véz 1, até o Véz 7. Vou ler aqui na nova, almeida atualizada, um trecho de Apocalipse. Claro, aquela carta que João envia também a igreja de Efezu…</t>
         </is>
       </c>
-      <c r="K214" s="2" t="inlineStr">
+      <c r="K214" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-realidade-da-igreja</t>
         </is>
       </c>
-      <c r="L214" s="2" t="inlineStr">
+      <c r="L214" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=tfantqpgCME</t>
         </is>
@@ -12797,7 +13006,7 @@
         </is>
       </c>
       <c r="J215" s="4" t="n"/>
-      <c r="L215" s="2" t="inlineStr">
+      <c r="L215" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=FHPHIvSrL9M</t>
         </is>
@@ -12833,7 +13042,7 @@
         </is>
       </c>
       <c r="J216" s="4" t="n"/>
-      <c r="L216" s="2" t="inlineStr">
+      <c r="L216" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=GaPoGvwFUr0</t>
         </is>
@@ -12869,7 +13078,7 @@
         </is>
       </c>
       <c r="J217" s="4" t="n"/>
-      <c r="L217" s="2" t="inlineStr">
+      <c r="L217" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=eLvum_z7Z_4</t>
         </is>
@@ -12905,7 +13114,7 @@
         </is>
       </c>
       <c r="J218" s="4" t="n"/>
-      <c r="L218" s="2" t="inlineStr">
+      <c r="L218" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=q-GHhd4dO7E</t>
         </is>
@@ -12941,7 +13150,7 @@
         </is>
       </c>
       <c r="J219" s="4" t="n"/>
-      <c r="L219" s="2" t="inlineStr">
+      <c r="L219" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=fc8qbdZEx1g</t>
         </is>
@@ -12991,12 +13200,12 @@
           <t>…om dia irmãos! Vamos abrir as nossas bíblas no Evangelho de Mateus. Evangelho de Mateus, Capítulo 5. Mateus, Capítulo 5, vamos ler dos versos 13 até 16. Esse é o nosso texto chave, nós vamos ler outros textos, mas esse é o nos…</t>
         </is>
       </c>
-      <c r="K220" s="2" t="inlineStr">
+      <c r="K220" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/um-povo-para-o-seu-nome-guilherme-de-carvalho</t>
         </is>
       </c>
-      <c r="L220" s="2" t="inlineStr">
+      <c r="L220" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=3O4P_L7TzRc</t>
         </is>
@@ -13051,12 +13260,12 @@
           <t>…ralmente, de Jonas em quatro sermões, eu padrão a esse, né? Jonas, se muito, segundo, pastor foi meu radical e preguem cinco, preguem seis sermões do Livro de Jonas. A gente teve um tempo que a gente teve 17 sermões no Livro…</t>
         </is>
       </c>
-      <c r="K221" s="2" t="inlineStr">
+      <c r="K221" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/a-improvavel-misericordia-de-deus</t>
         </is>
       </c>
-      <c r="L221" s="2" t="inlineStr">
+      <c r="L221" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=_1yXSaX0bUI</t>
         </is>
@@ -13111,12 +13320,12 @@
           <t>…interesses de Cristo e para o bem do mundo. A gente vai ler Jonas 2, a gente vai ler do vesículo 10 até a primeira metade do vesículo 3 do capítulo 3. Jonas 2, 10 até a primeira metade de Jonas 3, 3. E o Senhor falou ao peixe…</t>
         </is>
       </c>
-      <c r="K222" s="2" t="inlineStr">
+      <c r="K222" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/como-nasce-um-missionario</t>
         </is>
       </c>
-      <c r="L222" s="2" t="inlineStr">
+      <c r="L222" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=adM0wXPiuFU</t>
         </is>
@@ -13161,12 +13370,12 @@
           <t>…, na sua leitura bíblica. Você pode pensar, por exemplo, em versículos isolados e a busca por textos provas para chegar a uma conclusão teológica. Então, hoje para você pergunto me der aí, base bíblica para batismo de crianças, e…</t>
         </is>
       </c>
-      <c r="K223" s="2" t="inlineStr">
+      <c r="K223" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/teologue-i-forum-de-cosmovisao-crista-parte-1</t>
         </is>
       </c>
-      <c r="L223" s="2" t="inlineStr">
+      <c r="L223" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=rxX6xmuldVk</t>
         </is>
@@ -13211,12 +13420,12 @@
           <t>…alando de reparar e receber verdade a partir da criação. Em levitico 13, por exemplo, a gente tem a necessidade de examinar alguém se ele está doente ou não. E você não tem uma revelação que diga se fulando, é doente ou se fulando…</t>
         </is>
       </c>
-      <c r="K224" s="2" t="inlineStr">
+      <c r="K224" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/teologue-i-forum-de-cosmovisao-crista-parte-2</t>
         </is>
       </c>
-      <c r="L224" s="2" t="inlineStr">
+      <c r="L224" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=yD7dmi5QjEE</t>
         </is>
@@ -13261,12 +13470,12 @@
           <t>…estava compartilhando aqui as bases, porque falando sobre o capitulo 14 de primeira corintos, e eu ele enquei que um dos problemas identificados na igreja de corinto quanto a oração em língua seja ela, a oração espiritual ou out…</t>
         </is>
       </c>
-      <c r="K225" s="2" t="inlineStr">
+      <c r="K225" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/teologue-i-forum-de-cosmovisao-crista-parte-3</t>
         </is>
       </c>
-      <c r="L225" s="2" t="inlineStr">
+      <c r="L225" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-6n7zucd03c</t>
         </is>
@@ -13307,12 +13516,12 @@
         </is>
       </c>
       <c r="J226" s="4" t="inlineStr"/>
-      <c r="K226" s="2" t="inlineStr">
+      <c r="K226" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/teologue-i-forum-de-cosmovisao-crista-parte-4</t>
         </is>
       </c>
-      <c r="L226" s="2" t="inlineStr">
+      <c r="L226" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=eivKZFF3FbU</t>
         </is>
@@ -13352,12 +13561,12 @@
           <t>…uitos, que nós poderemos citar de Datoranôme 24, que diz no versículo 17 e 18, não perver tão o direito do estrangeiro e do órfão, nem tome em pêmora a roupa da viúva. Lembre-se de que vocês foram escravos no Egito e de que o Sen…</t>
         </is>
       </c>
-      <c r="K227" s="2" t="inlineStr">
+      <c r="K227" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-servico-cristao-podcast-ser-familia-episodio-01</t>
         </is>
       </c>
-      <c r="L227" s="2" t="inlineStr">
+      <c r="L227" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=3yz4wGci93c</t>
         </is>
@@ -13393,12 +13602,12 @@
         </is>
       </c>
       <c r="J228" s="4" t="inlineStr"/>
-      <c r="K228" s="2" t="inlineStr">
+      <c r="K228" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/ser-familia-podcast-ser-familia-episodio-02</t>
         </is>
       </c>
-      <c r="L228" s="2" t="inlineStr">
+      <c r="L228" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=tuzYv-6UO9A</t>
         </is>
@@ -13434,12 +13643,12 @@
         </is>
       </c>
       <c r="J229" s="4" t="inlineStr"/>
-      <c r="K229" s="2" t="inlineStr">
+      <c r="K229" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/imigrando-para-o-brasil-podcast-ser-familia-episodio-03</t>
         </is>
       </c>
-      <c r="L229" s="2" t="inlineStr">
+      <c r="L229" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jC7c6D1cSLM</t>
         </is>
@@ -13479,12 +13688,12 @@
           <t>…o que era algo simbólico, principalmente com o mais naquele versículo em Fésio 6, que diz que calçados da preparação do evangelho da paz. Então, se eu estava fabricando sapatos, estava fabricando calçados de preparação, fabricar…</t>
         </is>
       </c>
-      <c r="K230" s="2" t="inlineStr">
+      <c r="K230" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/episodio-4-podcast-ser-familia</t>
         </is>
       </c>
-      <c r="L230" s="2" t="inlineStr">
+      <c r="L230" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=15nWFNiq9Uo</t>
         </is>
@@ -13520,12 +13729,12 @@
         </is>
       </c>
       <c r="J231" s="4" t="inlineStr"/>
-      <c r="K231" s="2" t="inlineStr">
+      <c r="K231" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/missionario-em-empresas-podcast-ser-familia-episodio-5</t>
         </is>
       </c>
-      <c r="L231" s="2" t="inlineStr">
+      <c r="L231" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=NfCVhv1xcgQ</t>
         </is>
@@ -13566,12 +13775,12 @@
         </is>
       </c>
       <c r="J232" s="4" t="inlineStr"/>
-      <c r="K232" s="2" t="inlineStr">
+      <c r="K232" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/liturgia-do-ordinario-vanessa-belmonte-encontro-de-mulheres</t>
         </is>
       </c>
-      <c r="L232" s="2" t="inlineStr">
+      <c r="L232" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=8bRB2OrOaNE</t>
         </is>
@@ -13621,12 +13830,12 @@
           <t>…dos, vou abrir a palavra do Senhor, para lhe hermos juntos. Eclesiastes, capítulo 3, a partir do versículo 1, se você tiver sua Bíblia, pode abrir comigo. Eclesiastes, capítulo 3. Vocês têm estudado essa carta juntos, né? Eu vou le…</t>
         </is>
       </c>
-      <c r="K233" s="2" t="inlineStr">
+      <c r="K233" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/cristo-e-o-tempo-vanessa-belmonte-eclesiastes-31-8-serie-vanitas-vanitatum</t>
         </is>
       </c>
-      <c r="L233" s="2" t="inlineStr">
+      <c r="L233" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=CKbdIexbGNk</t>
         </is>
@@ -13672,12 +13881,12 @@
         </is>
       </c>
       <c r="J234" s="4" t="inlineStr"/>
-      <c r="K234" s="2" t="inlineStr">
+      <c r="K234" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/o-evangelho-da-igreja-paulo-borges-jr-com-todos-os-santos</t>
         </is>
       </c>
-      <c r="L234" s="2" t="inlineStr">
+      <c r="L234" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=OOcRJ22joWo</t>
         </is>
@@ -13723,12 +13932,12 @@
         </is>
       </c>
       <c r="J235" s="4" t="inlineStr"/>
-      <c r="K235" s="2" t="inlineStr">
+      <c r="K235" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/uns-aos-outros-paulo-borges-jr-com-todos-os-santos</t>
         </is>
       </c>
-      <c r="L235" s="2" t="inlineStr">
+      <c r="L235" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=tpUb7nO-t6o</t>
         </is>
@@ -13774,12 +13983,12 @@
         </is>
       </c>
       <c r="J236" s="4" t="inlineStr"/>
-      <c r="K236" s="2" t="inlineStr">
+      <c r="K236" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/identidade-natureza-e-proposito-paulo-borges-jr-com-todos-os-santos</t>
         </is>
       </c>
-      <c r="L236" s="2" t="inlineStr">
+      <c r="L236" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Hw27wxncTvs</t>
         </is>
@@ -13834,12 +14043,12 @@
           <t>…cisando de entendimento. Abra sua Bíblia Lainha e Fésios no capítulo 3 e Paulo ele está orando pela igreja. É interessante que a carta de Paulo aos Efeios é uma carta devotional. Glória a Deus, amém? Não é, é uma carta devotiona…</t>
         </is>
       </c>
-      <c r="K237" s="2" t="inlineStr">
+      <c r="K237" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20191203-paulo-borges-audio</t>
         </is>
       </c>
-      <c r="L237" s="2" t="inlineStr">
+      <c r="L237" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=N4qmp--42eA</t>
         </is>
@@ -13894,12 +14103,12 @@
           <t>…coisas coberam. Glória a Deus. Então abra sua bíblia lá em Ephesios no capítulo 4. E dando sequência aquilo que a gente compartilhou ontem. A gente terminou ontem falando aquele esforço pela comunhão, o esforço, pela unidade. É…</t>
         </is>
       </c>
-      <c r="K238" s="2" t="inlineStr">
+      <c r="K238" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/20190204-paulo-borges-audio</t>
         </is>
       </c>
-      <c r="L238" s="2" t="inlineStr">
+      <c r="L238" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=vjtgn-z6wyo</t>
         </is>
@@ -13954,12 +14163,12 @@
           <t>…você ouvirá agora o Ciro da Família dos Cretes. Ficando aos corintos, capítulos noves, versículos cinco. O opós-lo palo de esportanto, eu joguei conveniente, dependendo a versão, como NVEI, achei necessário, recomendar aos ir…</t>
         </is>
       </c>
-      <c r="K239" s="2" t="inlineStr">
+      <c r="K239" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/generosidade-extravagante-luciano-subira</t>
         </is>
       </c>
-      <c r="L239" s="2" t="inlineStr">
+      <c r="L239" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=gFXh2HJpobU</t>
         </is>
@@ -14014,12 +14223,12 @@
           <t>…supreender com o que Deus vai te ensinar. Abra sua bible e Mateus no capítulo 13 e no versículo 52. A ideia que hoje é num dia ideal para compartilhar muito aquilo que define o nosso DNA. Eu poderia falar muito de amor pelo S…</t>
         </is>
       </c>
-      <c r="K240" s="2" t="inlineStr">
+      <c r="K240" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/coisas-novas-e-coisas-velhaslucianosubira</t>
         </is>
       </c>
-      <c r="L240" s="2" t="inlineStr">
+      <c r="L240" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=E3KyrLjxXDU</t>
         </is>
@@ -14074,723 +14283,483 @@
           <t>…sabe o ton de voz de falar com eles. Abra comigo rapidinho, Proverb 24, verso 3. Proverb 24, verso 3. Te mostrar um texto interessante aqui, sei ser a reparou. Proverb 24, verso 3. Desacim, abre comigo, Proverb, capítulo 24,…</t>
         </is>
       </c>
-      <c r="K241" s="2" t="inlineStr">
+      <c r="K241" s="4" t="inlineStr">
         <is>
           <t>https://soundcloud.com/familiadosquecreem/douglas-goncalves</t>
         </is>
       </c>
-      <c r="L241" s="2" t="inlineStr">
+      <c r="L241" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=vLmkfMKVv7A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L241"/>
+  <autoFilter ref="A1:M241"/>
   <dataValidations count="1">
     <dataValidation sqref="I2:I241" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Confirmado (anunciado no sermão),Provável — revisar,Incerto — revisar,Temático / sem texto único anunciado,Panorama do livro (introdução à série),Revisado manualmente"</formula1>
+      <formula1>"Confirmado (anunciado no sermão),Provável — revisar,Incerto — revisar,Temático / sem texto único anunciado,Panorama do livro (introdução à série),Revisado manualmente,Confirmado (transcrição + NotebookLM),Incerto — revisar (fontes divergem)"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K195" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K196" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K197" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K209" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K210" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K211" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K212" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K221" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K222" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K223" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K224" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K225" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K226" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K227" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K229" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K230" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K231" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K232" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K233" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K234" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K235" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K236" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K237" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K238" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K239" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K240" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L149" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K150" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L150" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K151" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L151" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K152" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L152" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K153" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L153" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K154" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L154" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K155" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L155" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K156" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L156" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K157" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L157" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K158" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L158" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K159" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L159" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K160" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L160" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K161" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L161" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K162" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L162" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K163" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L163" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K164" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L164" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L165" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L166" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L167" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L168" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L169" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L170" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L171" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L172" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L173" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L174" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L175" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L176" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L177" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L178" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L179" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L180" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L181" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L182" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L183" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L184" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L185" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L186" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L187" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L188" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L189" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L190" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K191" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L191" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K192" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L192" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K193" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L193" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K194" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L194" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K195" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L195" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K196" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L196" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K197" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L197" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L198" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K199" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L199" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K200" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L200" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K201" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L201" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K202" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L202" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K203" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L203" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K204" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L204" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K205" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L205" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L206" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L207" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L208" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K209" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L209" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K210" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L210" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K211" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L211" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K212" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L212" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K213" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L213" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K214" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L214" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L215" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L216" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L217" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L218" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L219" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K220" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L220" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K221" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L221" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K222" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L222" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K223" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L223" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K224" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L224" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K225" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L225" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K226" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L226" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K227" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L227" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K228" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L228" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K229" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L229" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K230" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L230" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K231" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L231" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K232" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L232" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K233" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L233" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K234" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L234" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K235" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L235" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K236" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L236" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K237" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L237" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K238" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L238" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K239" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L239" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K240" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L240" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K241" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L241" r:id="rId458"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14815,9 +14784,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>

--- a/sermoes/sermoes_fdqc_preenchida.xlsx
+++ b/sermoes/sermoes_fdqc_preenchida.xlsx
@@ -10351,15 +10351,25 @@
           <t>~2019</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Rt 1–4</t>
+        </is>
+      </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Sem áudio próprio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J165" s="4" t="n"/>
       <c r="L165" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=jFc2sOuPvys</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Rute 1:1-21; 2:5-12; 3:9-12; 4:6-18</t>
         </is>
       </c>
     </row>
@@ -11208,15 +11218,25 @@
           <t>~2018</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Ef 1.1-14</t>
+        </is>
+      </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J179" s="4" t="n"/>
       <c r="L179" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=qXL1mkpAtu4</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Efésios 1:1-14; Efésios 2:10, 22; Ezequiel 36:25-28</t>
         </is>
       </c>
     </row>
@@ -11249,15 +11269,25 @@
           <t>~2018</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>1Co 11.17-34; Rm 12</t>
+        </is>
+      </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J180" s="4" t="n"/>
       <c r="L180" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=z_MSUPJTuNU</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>1 Coríntios 11:17-34; Romanos 12:1-21 (resposta quase idêntica à de "Para que nos reunimos?" — conferir)</t>
         </is>
       </c>
     </row>
@@ -11290,15 +11320,25 @@
           <t>~2018</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Mt 16.13-19</t>
+        </is>
+      </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J181" s="4" t="n"/>
       <c r="L181" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=9Lc8RamwSfY</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Mateus 16:13-19; 1 Timóteo 3:15; Efésios 3:9-10; Atos 20:24; Lucas 4:43; Apocalipse 14:6; Números 16:41-50</t>
         </is>
       </c>
     </row>
@@ -11331,15 +11371,25 @@
           <t>~2018</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Ef 4.1-16</t>
+        </is>
+      </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J182" s="4" t="n"/>
       <c r="L182" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=URLxnlIMpvc</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Efésios 4:1-16; Efésios 1:18; 3:18-19; 2 Pedro 1:3-11</t>
         </is>
       </c>
     </row>
@@ -11372,15 +11422,25 @@
           <t>~2018</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Ap 3.1-3</t>
+        </is>
+      </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J183" s="4" t="n"/>
       <c r="L183" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=y5RaaLVs4FY</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Apocalipse 3:1-3; Gênesis 6:9; Mateus 24:38; 1 Tessalonicenses 5:3; 2 Coríntios 5:17-20</t>
         </is>
       </c>
     </row>
@@ -11413,15 +11473,25 @@
           <t>~2018</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Gn 4.17-24; Jr 29.4-7</t>
+        </is>
+      </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J184" s="4" t="n"/>
       <c r="L184" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=37Ctc3FJ46k</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Gênesis 4:17-24; Mateus 9:35-38; Jeremias 29:4-7; Hebreus 11:8-10</t>
         </is>
       </c>
     </row>
@@ -11454,15 +11524,25 @@
           <t>~2018</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>1Co 11.17-34; Rm 12.1-2</t>
+        </is>
+      </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J185" s="4" t="n"/>
       <c r="L185" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=T_Df7pxWru4</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>1 Coríntios 11:17-34; Romanos 12:1-2</t>
         </is>
       </c>
     </row>
@@ -11490,15 +11570,25 @@
           <t>~dez/2025</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Lc 2.8-20</t>
+        </is>
+      </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J186" s="4" t="n"/>
       <c r="L186" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=LVp1npjJ7Qk</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Lucas 2:8-20; Gênesis 3:15; Isaías 9:2-6; Jeremias 29:13</t>
         </is>
       </c>
     </row>
@@ -11526,15 +11616,25 @@
           <t>~2024</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Is 7.14; Mt 1.23; Is 53</t>
+        </is>
+      </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Temático / vários textos</t>
         </is>
       </c>
       <c r="J187" s="4" t="n"/>
       <c r="L187" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=G2Ggf1Mr4TI</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Isaías 7:14 / Mateus 1:23; Isaías 53; panorama da história da redenção (cantata)</t>
         </is>
       </c>
     </row>
@@ -11567,15 +11667,25 @@
           <t>~dez/2024</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Is 9.6</t>
+        </is>
+      </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J188" s="4" t="n"/>
       <c r="L188" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=Te5QQIv4vuA</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Isaías 9:6</t>
         </is>
       </c>
     </row>
@@ -11603,15 +11713,25 @@
           <t>~dez/2023</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Jo 1.1-3; Mt 1.21; Ap 21.1-4 (vários textos)</t>
+        </is>
+      </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Temático / vários textos</t>
         </is>
       </c>
       <c r="J189" s="4" t="n"/>
       <c r="L189" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=rnyN95QCvDg</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>João 1:1-3; 2 Timóteo 1:8-10; Romanos 3:23; Mateus 1:21; 2:1-2; Tito 2:11-13; Apocalipse 21:1-4</t>
         </is>
       </c>
     </row>
@@ -11644,15 +11764,25 @@
           <t>~2023</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Mt 1.18-23; Lc 1.26-38</t>
+        </is>
+      </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J190" s="4" t="n"/>
       <c r="L190" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=rpUmvWkIKsw</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Mateus 1:1-17; 1:18-23; Lucas 1:26-38; 2:10-14</t>
         </is>
       </c>
     </row>
@@ -12090,15 +12220,25 @@
           <t>Datas especiais e sermões avulsos</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>1Co 15.21-28</t>
+        </is>
+      </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J198" s="4" t="n"/>
       <c r="L198" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=-roaRFAQ0zM</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>1 Coríntios 15:21-28; 1 Coríntios 11; Romanos 3:23</t>
         </is>
       </c>
     </row>
@@ -12552,15 +12692,25 @@
           <t>~2019-2020</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sl 89</t>
+        </is>
+      </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Provável — revisar</t>
         </is>
       </c>
       <c r="J206" s="4" t="n"/>
       <c r="L206" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=f-66VyYLImk</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Salmo 89:1-52; Isaías 26:9; Salmos 73 e 74; Jeremias 29:11</t>
         </is>
       </c>
     </row>
@@ -12593,15 +12743,25 @@
           <t>~2019-2020</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Is 26.9; Am 3.6; Rm 5.8-9 (vários textos)</t>
+        </is>
+      </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Temático / vários textos</t>
         </is>
       </c>
       <c r="J207" s="4" t="n"/>
       <c r="L207" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=kpqtWTruD-0</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Isaías 26:9; Amós 3:6; Romanos 3:23; 5:8-9; 1 Coríntios 15:19</t>
         </is>
       </c>
     </row>
@@ -12634,15 +12794,25 @@
           <t>~2019-2020</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>2Tm 1.7; Mt 24.6; Mt 13 (vários textos)</t>
+        </is>
+      </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Temático / vários textos</t>
         </is>
       </c>
       <c r="J208" s="4" t="n"/>
       <c r="L208" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=yMJ11VbkhRU</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2 Timóteo 1:7; Mateus 24:6; Mateus 13; Tito 2:13; 2 Pedro 3:12</t>
         </is>
       </c>
     </row>
@@ -13000,15 +13170,25 @@
           <t>Pregadores convidados, conferências e outros conteúdos</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sl 96.1-13</t>
+        </is>
+      </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Não se aplica (palestra/podcast)</t>
         </is>
       </c>
       <c r="J215" s="4" t="n"/>
       <c r="L215" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=FHPHIvSrL9M</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Salmo 96:1-13 (paralelo: 1 Crônicas 16:23-33)</t>
         </is>
       </c>
     </row>
@@ -13038,13 +13218,18 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Não se aplica (palestra/podcast)</t>
         </is>
       </c>
       <c r="J216" s="4" t="n"/>
       <c r="L216" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=GaPoGvwFUr0</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Painel de perguntas e respostas (sem texto base)</t>
         </is>
       </c>
     </row>
@@ -13072,15 +13257,25 @@
           <t>~2024</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>2Ts 2.1-4; Hb 11.13-16</t>
+        </is>
+      </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Não se aplica (palestra/podcast)</t>
         </is>
       </c>
       <c r="J217" s="4" t="n"/>
       <c r="L217" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=eLvum_z7Z_4</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2 Tessalonicenses 2:1-4; 1 Pedro; Hebreus 11:13-16</t>
         </is>
       </c>
     </row>
@@ -13108,15 +13303,25 @@
           <t>~2024</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Rm 1.18-25; 12.2</t>
+        </is>
+      </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Não se aplica (palestra/podcast)</t>
         </is>
       </c>
       <c r="J218" s="4" t="n"/>
       <c r="L218" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=q-GHhd4dO7E</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Romanos 1:18-25; Romanos 12:2</t>
         </is>
       </c>
     </row>
@@ -13146,13 +13351,18 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Sem áudio no podcast — usar NotebookLM</t>
+          <t>Não se aplica (palestra/podcast)</t>
         </is>
       </c>
       <c r="J219" s="4" t="n"/>
       <c r="L219" s="4" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=fc8qbdZEx1g</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Palestra temática (sem texto base)</t>
         </is>
       </c>
     </row>
@@ -14771,7 +14981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -14784,7 +14994,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -14831,6 +15040,13 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>• Linhas sem áudio no podcast: usar o NotebookLM com o link do YouTube (prompt no README).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>• Coluna "NotebookLM": resposta do NotebookLM. Para os 22 vídeos sem áudio no podcast, ele é a única fonte, por isso o status é no máximo "Provável".</t>
         </is>
       </c>
     </row>
